--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EA1CD3C-0CCB-4FAE-B6DF-141EAF33FD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B01D778B-4818-4106-85A4-E555E87EB005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8791,7 +8791,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6CFEDC-E56D-460B-9579-798B670AC720}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42168D2D-1EBA-49F3-8FC3-578FE3002CD8}">
   <dimension ref="B2:AI1212"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B01D778B-4818-4106-85A4-E555E87EB005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7442BADB-1DA6-4E57-BA74-32A31D5393DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8791,7 +8791,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42168D2D-1EBA-49F3-8FC3-578FE3002CD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C071516-1C86-4BB8-8C68-83EBB61B628C}">
   <dimension ref="B2:AI1212"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7442BADB-1DA6-4E57-BA74-32A31D5393DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C5B5DAD-6FD8-4810-95A6-671A52DAB782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8791,7 +8791,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C071516-1C86-4BB8-8C68-83EBB61B628C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8833A1CA-074C-41A7-8BA9-BD821D3D9597}">
   <dimension ref="B2:AI1212"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18FDC9FB-C613-48F1-A82B-24228156AB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C710D076-0ADB-4381-895A-63E201C9D41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E27C26C-D581-4112-8621-FC4D69633E8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79125B68-3B50-4CB7-B625-7B2A6BBBF2B9}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C710D076-0ADB-4381-895A-63E201C9D41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03AE59D1-1D78-4D87-8FF0-FF855CC8B4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79125B68-3B50-4CB7-B625-7B2A6BBBF2B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD09DC6-2415-4511-AF17-A2A25251F71F}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03AE59D1-1D78-4D87-8FF0-FF855CC8B4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C85936F-BF8B-44FB-9A57-EA611D10E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD09DC6-2415-4511-AF17-A2A25251F71F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB96CD3-4ABB-4761-B735-4048540EA063}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C85936F-BF8B-44FB-9A57-EA611D10E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F1BC68D-5F0E-40F8-ABE2-143DC4F3C169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB96CD3-4ABB-4761-B735-4048540EA063}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54F9E6C-A544-4B8A-B627-F00388A0F458}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F1BC68D-5F0E-40F8-ABE2-143DC4F3C169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE7F78AE-88D7-45F5-B2BC-ACEB9BE4BD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54F9E6C-A544-4B8A-B627-F00388A0F458}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AAE7DDA-3772-42E6-B453-C6542AC6972B}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE7F78AE-88D7-45F5-B2BC-ACEB9BE4BD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5721D32B-94D5-4AEB-9ED4-77DDD19510E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AAE7DDA-3772-42E6-B453-C6542AC6972B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888E8539-A18B-437A-B092-2E59F53DB23D}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5721D32B-94D5-4AEB-9ED4-77DDD19510E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C61B41A-B17F-46A9-B300-BD4B3728EF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888E8539-A18B-437A-B092-2E59F53DB23D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B2C942-F7DF-4C5F-A08E-B75B1807A797}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C61B41A-B17F-46A9-B300-BD4B3728EF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F4EA3B-10EA-4C63-A421-15C3A7E24578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B2C942-F7DF-4C5F-A08E-B75B1807A797}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B9962B-B911-4394-A026-80DBC10C4310}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F4EA3B-10EA-4C63-A421-15C3A7E24578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C94E34B-8008-42C7-BCC5-F109885241B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B9962B-B911-4394-A026-80DBC10C4310}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C771B8C4-B749-4754-A5D3-9ADF577FD0F4}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C94E34B-8008-42C7-BCC5-F109885241B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A4CACF-0B1F-43E1-AE6B-81404DC64CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C771B8C4-B749-4754-A5D3-9ADF577FD0F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82208C14-AF33-4E7E-87E2-1AF4958095EB}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A4CACF-0B1F-43E1-AE6B-81404DC64CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0706E47C-68DC-4FD8-BE92-F993DB49153B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82208C14-AF33-4E7E-87E2-1AF4958095EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532CF127-9B26-4947-9982-F39DB9805C7D}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0706E47C-68DC-4FD8-BE92-F993DB49153B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C64EAEEE-2F9A-4C60-ADDD-88B64C65E659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532CF127-9B26-4947-9982-F39DB9805C7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D0529-2132-4F84-84EF-CD0FB2F5887D}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C64EAEEE-2F9A-4C60-ADDD-88B64C65E659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A430ECD2-54E6-4A60-8581-F2FCA6E23815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D0529-2132-4F84-84EF-CD0FB2F5887D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A27BCC-2757-4426-8A06-81C7CA18147F}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A430ECD2-54E6-4A60-8581-F2FCA6E23815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F827B11A-D4AF-4A19-A6A5-B38A710055FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A27BCC-2757-4426-8A06-81C7CA18147F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{974AECE2-2269-43F3-9A6C-B46EC739352F}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F827B11A-D4AF-4A19-A6A5-B38A710055FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B84B4168-D91C-4CB3-9D8A-A09809197267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{974AECE2-2269-43F3-9A6C-B46EC739352F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D3176C-7C1B-4D64-9B94-222C36406136}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B84B4168-D91C-4CB3-9D8A-A09809197267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84CB1E2F-AE3A-4603-987C-5220ED25B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D3176C-7C1B-4D64-9B94-222C36406136}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137F0027-12DF-4B82-B4BF-6CEDA34C74E3}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84CB1E2F-AE3A-4603-987C-5220ED25B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D9E6982-277C-40E0-98B7-2BA0719B198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137F0027-12DF-4B82-B4BF-6CEDA34C74E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7F1E96-F4CB-412D-8A55-45F70C0FF273}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D9E6982-277C-40E0-98B7-2BA0719B198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DBBDE29-5C7A-4853-B08D-B30F90EB4487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7F1E96-F4CB-412D-8A55-45F70C0FF273}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB493385-A917-4BC0-AB3B-43A9F6158CA0}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DBBDE29-5C7A-4853-B08D-B30F90EB4487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{392A2593-E2B5-45CC-B5DC-FD585078CD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB493385-A917-4BC0-AB3B-43A9F6158CA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4575DD9F-F944-4718-BF51-6A5181E223A9}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{392A2593-E2B5-45CC-B5DC-FD585078CD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{477270A4-0A7B-4271-94C4-F0F2474ED827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4575DD9F-F944-4718-BF51-6A5181E223A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DD232F-F07E-4B93-8799-76AF00AA85F0}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{477270A4-0A7B-4271-94C4-F0F2474ED827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA40CC75-40EF-4105-91B4-6D986C4277B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DD232F-F07E-4B93-8799-76AF00AA85F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD5FFD7-B0F9-4670-AD0F-DCFB7AEEF230}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA40CC75-40EF-4105-91B4-6D986C4277B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0D391F4-97CE-4907-9370-2AF66D2EFD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6150,7 +6150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD5FFD7-B0F9-4670-AD0F-DCFB7AEEF230}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80F6684-870F-4EEB-9D0B-0637ACE53E45}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0D391F4-97CE-4907-9370-2AF66D2EFD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4C5BB33-A62F-4D44-B544-5F8D23550F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8221" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8221" uniqueCount="1929">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -4845,211 +4845,457 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_w303915533-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w76709660-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w59462263-380</t>
+    <t>EN_Hydro_ITA-1_w76709660-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w76709660-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w76709660-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w59462263-380</t>
   </si>
   <si>
     <t>e_w59462263-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w338753171-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IT116-380</t>
+    <t>EN_Hydro_ITA-2_w59462263-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w59462263-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w338753171-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w338753171-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w338753171-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT116-380</t>
   </si>
   <si>
     <t>e_IT116-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT10-380</t>
+    <t>EN_Hydro_ITA-2_IT116-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT116-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT10-380</t>
   </si>
   <si>
     <t>e_IT10-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT71-380</t>
+    <t>EN_Hydro_ITA-2_IT10-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT10-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT71-380</t>
   </si>
   <si>
     <t>e_IT71-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w114931087-380</t>
+    <t>EN_Hydro_ITA-2_IT71-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT71-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w114931087-380</t>
   </si>
   <si>
     <t>e_w114931087-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w61712456-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w64200868-380</t>
+    <t>EN_Hydro_ITA-2_w114931087-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w114931087-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w61712456-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w61712456-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w61712456-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w64200868-380</t>
   </si>
   <si>
     <t>e_w64200868-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT31-380</t>
+    <t>EN_Hydro_ITA-2_w64200868-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w64200868-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT31-380</t>
   </si>
   <si>
     <t>e_IT31-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w42206116-380</t>
+    <t>EN_Hydro_ITA-2_IT31-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT31-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w42206116-380</t>
   </si>
   <si>
     <t>e_w42206116-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT30-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w108020416-380</t>
+    <t>EN_Hydro_ITA-2_w42206116-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w42206116-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT30-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_IT30-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT30-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w108020416-380</t>
   </si>
   <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w155791516-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IT21-380</t>
+    <t>EN_Hydro_ITA-2_w108020416-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w108020416-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w155791516-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w155791516-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w155791516-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT21-380</t>
   </si>
   <si>
     <t>e_IT21-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w1100665914-380</t>
+    <t>EN_Hydro_ITA-2_IT21-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT21-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w1100665914-380</t>
   </si>
   <si>
     <t>e_w1100665914-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w419423704-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w75602396-380</t>
+    <t>EN_Hydro_ITA-2_w1100665914-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w1100665914-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w419423704-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w419423704-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w419423704-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w75602396-380</t>
   </si>
   <si>
     <t>e_w75602396-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w339706878-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w72466334-380</t>
+    <t>EN_Hydro_ITA-2_w75602396-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w75602396-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w339706878-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w339706878-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w339706878-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w72466334-380</t>
   </si>
   <si>
     <t>e_w72466334-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT36-380</t>
+    <t>EN_Hydro_ITA-2_w72466334-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w72466334-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT36-380</t>
   </si>
   <si>
     <t>e_IT36-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w104359058-380</t>
+    <t>EN_Hydro_ITA-2_IT36-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT36-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w104359058-380</t>
   </si>
   <si>
     <t>e_w104359058-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w82083756-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IT53-380</t>
+    <t>EN_Hydro_ITA-2_w104359058-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w104359058-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w82083756-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w82083756-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w82083756-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT53-380</t>
   </si>
   <si>
     <t>e_IT53-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w61157826-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w116517585-380</t>
+    <t>EN_Hydro_ITA-2_IT53-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT53-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w61157826-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w61157826-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w61157826-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w116517585-380</t>
   </si>
   <si>
     <t>e_w116517585-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w339703159-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IT7-380</t>
+    <t>EN_Hydro_ITA-2_w116517585-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w116517585-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w339703159-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w339703159-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w339703159-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT7-380</t>
   </si>
   <si>
     <t>e_IT7-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT72-400</t>
+    <t>EN_Hydro_ITA-2_IT7-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT7-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT72-400</t>
   </si>
   <si>
     <t>e_IT72-400</t>
   </si>
   <si>
-    <t>EN_Hydro_w61626687-380</t>
+    <t>EN_Hydro_ITA-2_IT72-400</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT72-400</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w61626687-380</t>
   </si>
   <si>
     <t>e_w61626687-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w109588422-380</t>
+    <t>EN_Hydro_ITA-2_w61626687-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w61626687-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w109588422-380</t>
   </si>
   <si>
     <t>e_w109588422-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w110330925-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IT93-380</t>
+    <t>EN_Hydro_ITA-2_w109588422-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w109588422-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w110330925-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w110330925-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w110330925-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT93-380</t>
   </si>
   <si>
     <t>e_IT93-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w96190189-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_IT72-380</t>
+    <t>EN_Hydro_ITA-2_IT93-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT93-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w96190189-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w96190189-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w96190189-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT72-380</t>
   </si>
   <si>
     <t>e_IT72-380</t>
   </si>
   <si>
-    <t>EN_Hydro_w1137611914-380</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w144005863-380</t>
+    <t>EN_Hydro_ITA-2_IT72-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT72-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w1137611914-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w1137611914-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w1137611914-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w144005863-380</t>
   </si>
   <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT128-380</t>
+    <t>EN_Hydro_ITA-2_w144005863-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w144005863-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT128-380</t>
   </si>
   <si>
     <t>e_IT128-380</t>
   </si>
   <si>
-    <t>EN_Hydro_IT40-500</t>
+    <t>EN_Hydro_ITA-2_IT128-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT128-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT40-500</t>
   </si>
   <si>
     <t>e_IT40-500</t>
   </si>
   <si>
-    <t>EN_Hydro_IT71-400</t>
+    <t>EN_Hydro_ITA-2_IT40-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT40-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_IT71-400</t>
   </si>
   <si>
     <t>e_IT71-400</t>
   </si>
   <si>
-    <t>EN_Hydro_w491424937-380</t>
+    <t>EN_Hydro_ITA-2_IT71-400</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_IT71-400</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-1_w491424937-380</t>
   </si>
   <si>
     <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-2_w491424937-380</t>
+  </si>
+  <si>
+    <t>EN_Hydro_ITA-3_w491424937-380</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_w84696559-380</t>
@@ -6150,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80F6684-870F-4EEB-9D0B-0637ACE53E45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A0596EB-BC60-40BF-923C-A18B070195EA}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6286,22 +6532,22 @@
         <v>412</v>
       </c>
       <c r="AB4" t="s">
-        <v>1838</v>
+        <v>1920</v>
       </c>
       <c r="AC4" t="s">
-        <v>1840</v>
+        <v>1922</v>
       </c>
       <c r="AD4" t="s">
-        <v>1841</v>
+        <v>1923</v>
       </c>
       <c r="AE4" t="s">
-        <v>1842</v>
+        <v>1924</v>
       </c>
       <c r="AG4" t="s">
-        <v>1844</v>
+        <v>1926</v>
       </c>
       <c r="AH4" t="s">
-        <v>1845</v>
+        <v>1927</v>
       </c>
       <c r="AI4" t="s">
         <v>818</v>
@@ -6357,10 +6603,10 @@
         <v>818</v>
       </c>
       <c r="AA5" t="s">
-        <v>1837</v>
+        <v>1919</v>
       </c>
       <c r="AB5" t="s">
-        <v>1839</v>
+        <v>1921</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -6369,13 +6615,13 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>1843</v>
+        <v>1925</v>
       </c>
       <c r="AG5" t="s">
-        <v>1846</v>
+        <v>1928</v>
       </c>
       <c r="AH5" t="s">
-        <v>1845</v>
+        <v>1927</v>
       </c>
       <c r="AI5" t="s">
         <v>736</v>
@@ -27674,7 +27920,7 @@
         <v>92</v>
       </c>
       <c r="V720" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="W720" t="s">
         <v>754</v>
@@ -27688,7 +27934,7 @@
         <v>92</v>
       </c>
       <c r="V721" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="W721" t="s">
         <v>754</v>
@@ -27702,10 +27948,10 @@
         <v>92</v>
       </c>
       <c r="V722" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="W722" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="X722" t="s">
         <v>818</v>
@@ -27716,10 +27962,10 @@
         <v>92</v>
       </c>
       <c r="V723" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="W723" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="X723" t="s">
         <v>818</v>
@@ -27730,10 +27976,10 @@
         <v>92</v>
       </c>
       <c r="V724" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="W724" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="X724" t="s">
         <v>818</v>
@@ -27744,7 +27990,7 @@
         <v>92</v>
       </c>
       <c r="V725" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="W725" t="s">
         <v>1217</v>
@@ -27758,7 +28004,7 @@
         <v>92</v>
       </c>
       <c r="V726" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="W726" t="s">
         <v>1217</v>
@@ -27772,7 +28018,7 @@
         <v>92</v>
       </c>
       <c r="V727" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="W727" t="s">
         <v>1217</v>
@@ -27786,10 +28032,10 @@
         <v>92</v>
       </c>
       <c r="V728" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="W728" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="X728" t="s">
         <v>818</v>
@@ -27800,10 +28046,10 @@
         <v>92</v>
       </c>
       <c r="V729" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
       <c r="W729" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="X729" t="s">
         <v>818</v>
@@ -27814,10 +28060,10 @@
         <v>92</v>
       </c>
       <c r="V730" t="s">
-        <v>1577</v>
+        <v>1586</v>
       </c>
       <c r="W730" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="X730" t="s">
         <v>818</v>
@@ -27828,10 +28074,10 @@
         <v>92</v>
       </c>
       <c r="V731" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
       <c r="W731" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="X731" t="s">
         <v>818</v>
@@ -27842,10 +28088,10 @@
         <v>92</v>
       </c>
       <c r="V732" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="W732" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="X732" t="s">
         <v>818</v>
@@ -27856,10 +28102,10 @@
         <v>92</v>
       </c>
       <c r="V733" t="s">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="W733" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="X733" t="s">
         <v>818</v>
@@ -27870,10 +28116,10 @@
         <v>92</v>
       </c>
       <c r="V734" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="W734" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="X734" t="s">
         <v>818</v>
@@ -27884,10 +28130,10 @@
         <v>92</v>
       </c>
       <c r="V735" t="s">
-        <v>1581</v>
+        <v>1593</v>
       </c>
       <c r="W735" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="X735" t="s">
         <v>818</v>
@@ -27898,10 +28144,10 @@
         <v>92</v>
       </c>
       <c r="V736" t="s">
-        <v>1581</v>
+        <v>1594</v>
       </c>
       <c r="W736" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="X736" t="s">
         <v>818</v>
@@ -27912,10 +28158,10 @@
         <v>92</v>
       </c>
       <c r="V737" t="s">
-        <v>1583</v>
+        <v>1595</v>
       </c>
       <c r="W737" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="X737" t="s">
         <v>818</v>
@@ -27926,10 +28172,10 @@
         <v>92</v>
       </c>
       <c r="V738" t="s">
-        <v>1583</v>
+        <v>1597</v>
       </c>
       <c r="W738" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="X738" t="s">
         <v>818</v>
@@ -27940,10 +28186,10 @@
         <v>92</v>
       </c>
       <c r="V739" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="W739" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="X739" t="s">
         <v>818</v>
@@ -27954,7 +28200,7 @@
         <v>92</v>
       </c>
       <c r="V740" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="W740" t="s">
         <v>797</v>
@@ -27968,7 +28214,7 @@
         <v>92</v>
       </c>
       <c r="V741" t="s">
-        <v>1585</v>
+        <v>1600</v>
       </c>
       <c r="W741" t="s">
         <v>797</v>
@@ -27982,7 +28228,7 @@
         <v>92</v>
       </c>
       <c r="V742" t="s">
-        <v>1585</v>
+        <v>1601</v>
       </c>
       <c r="W742" t="s">
         <v>797</v>
@@ -27996,10 +28242,10 @@
         <v>92</v>
       </c>
       <c r="V743" t="s">
-        <v>1586</v>
+        <v>1602</v>
       </c>
       <c r="W743" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="X743" t="s">
         <v>818</v>
@@ -28010,10 +28256,10 @@
         <v>92</v>
       </c>
       <c r="V744" t="s">
-        <v>1586</v>
+        <v>1604</v>
       </c>
       <c r="W744" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="X744" t="s">
         <v>818</v>
@@ -28024,10 +28270,10 @@
         <v>92</v>
       </c>
       <c r="V745" t="s">
-        <v>1586</v>
+        <v>1605</v>
       </c>
       <c r="W745" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="X745" t="s">
         <v>818</v>
@@ -28038,10 +28284,10 @@
         <v>92</v>
       </c>
       <c r="V746" t="s">
-        <v>1588</v>
+        <v>1606</v>
       </c>
       <c r="W746" t="s">
-        <v>1589</v>
+        <v>1607</v>
       </c>
       <c r="X746" t="s">
         <v>818</v>
@@ -28052,10 +28298,10 @@
         <v>92</v>
       </c>
       <c r="V747" t="s">
-        <v>1588</v>
+        <v>1608</v>
       </c>
       <c r="W747" t="s">
-        <v>1589</v>
+        <v>1607</v>
       </c>
       <c r="X747" t="s">
         <v>818</v>
@@ -28066,10 +28312,10 @@
         <v>92</v>
       </c>
       <c r="V748" t="s">
-        <v>1588</v>
+        <v>1609</v>
       </c>
       <c r="W748" t="s">
-        <v>1589</v>
+        <v>1607</v>
       </c>
       <c r="X748" t="s">
         <v>818</v>
@@ -28080,10 +28326,10 @@
         <v>92</v>
       </c>
       <c r="V749" t="s">
-        <v>1590</v>
+        <v>1610</v>
       </c>
       <c r="W749" t="s">
-        <v>1591</v>
+        <v>1611</v>
       </c>
       <c r="X749" t="s">
         <v>818</v>
@@ -28094,10 +28340,10 @@
         <v>92</v>
       </c>
       <c r="V750" t="s">
-        <v>1590</v>
+        <v>1612</v>
       </c>
       <c r="W750" t="s">
-        <v>1591</v>
+        <v>1611</v>
       </c>
       <c r="X750" t="s">
         <v>818</v>
@@ -28108,10 +28354,10 @@
         <v>92</v>
       </c>
       <c r="V751" t="s">
-        <v>1590</v>
+        <v>1613</v>
       </c>
       <c r="W751" t="s">
-        <v>1591</v>
+        <v>1611</v>
       </c>
       <c r="X751" t="s">
         <v>818</v>
@@ -28122,7 +28368,7 @@
         <v>92</v>
       </c>
       <c r="V752" t="s">
-        <v>1592</v>
+        <v>1614</v>
       </c>
       <c r="W752" t="s">
         <v>811</v>
@@ -28136,7 +28382,7 @@
         <v>92</v>
       </c>
       <c r="V753" t="s">
-        <v>1592</v>
+        <v>1615</v>
       </c>
       <c r="W753" t="s">
         <v>811</v>
@@ -28150,7 +28396,7 @@
         <v>92</v>
       </c>
       <c r="V754" t="s">
-        <v>1592</v>
+        <v>1616</v>
       </c>
       <c r="W754" t="s">
         <v>811</v>
@@ -28164,10 +28410,10 @@
         <v>92</v>
       </c>
       <c r="V755" t="s">
-        <v>1593</v>
+        <v>1617</v>
       </c>
       <c r="W755" t="s">
-        <v>1594</v>
+        <v>1618</v>
       </c>
       <c r="X755" t="s">
         <v>818</v>
@@ -28178,10 +28424,10 @@
         <v>92</v>
       </c>
       <c r="V756" t="s">
-        <v>1593</v>
+        <v>1619</v>
       </c>
       <c r="W756" t="s">
-        <v>1594</v>
+        <v>1618</v>
       </c>
       <c r="X756" t="s">
         <v>818</v>
@@ -28192,10 +28438,10 @@
         <v>92</v>
       </c>
       <c r="V757" t="s">
-        <v>1593</v>
+        <v>1620</v>
       </c>
       <c r="W757" t="s">
-        <v>1594</v>
+        <v>1618</v>
       </c>
       <c r="X757" t="s">
         <v>818</v>
@@ -28206,7 +28452,7 @@
         <v>92</v>
       </c>
       <c r="V758" t="s">
-        <v>1595</v>
+        <v>1621</v>
       </c>
       <c r="W758" t="s">
         <v>788</v>
@@ -28220,7 +28466,7 @@
         <v>92</v>
       </c>
       <c r="V759" t="s">
-        <v>1595</v>
+        <v>1622</v>
       </c>
       <c r="W759" t="s">
         <v>788</v>
@@ -28234,7 +28480,7 @@
         <v>92</v>
       </c>
       <c r="V760" t="s">
-        <v>1595</v>
+        <v>1623</v>
       </c>
       <c r="W760" t="s">
         <v>788</v>
@@ -28248,10 +28494,10 @@
         <v>92</v>
       </c>
       <c r="V761" t="s">
-        <v>1596</v>
+        <v>1624</v>
       </c>
       <c r="W761" t="s">
-        <v>1597</v>
+        <v>1625</v>
       </c>
       <c r="X761" t="s">
         <v>818</v>
@@ -28262,10 +28508,10 @@
         <v>92</v>
       </c>
       <c r="V762" t="s">
-        <v>1596</v>
+        <v>1626</v>
       </c>
       <c r="W762" t="s">
-        <v>1597</v>
+        <v>1625</v>
       </c>
       <c r="X762" t="s">
         <v>818</v>
@@ -28276,10 +28522,10 @@
         <v>92</v>
       </c>
       <c r="V763" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="W763" t="s">
-        <v>1597</v>
+        <v>1625</v>
       </c>
       <c r="X763" t="s">
         <v>818</v>
@@ -28290,10 +28536,10 @@
         <v>92</v>
       </c>
       <c r="V764" t="s">
-        <v>1598</v>
+        <v>1628</v>
       </c>
       <c r="W764" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="X764" t="s">
         <v>818</v>
@@ -28304,10 +28550,10 @@
         <v>92</v>
       </c>
       <c r="V765" t="s">
-        <v>1598</v>
+        <v>1630</v>
       </c>
       <c r="W765" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="X765" t="s">
         <v>818</v>
@@ -28318,10 +28564,10 @@
         <v>92</v>
       </c>
       <c r="V766" t="s">
-        <v>1598</v>
+        <v>1631</v>
       </c>
       <c r="W766" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="X766" t="s">
         <v>818</v>
@@ -28332,7 +28578,7 @@
         <v>92</v>
       </c>
       <c r="V767" t="s">
-        <v>1600</v>
+        <v>1632</v>
       </c>
       <c r="W767" t="s">
         <v>1203</v>
@@ -28346,7 +28592,7 @@
         <v>92</v>
       </c>
       <c r="V768" t="s">
-        <v>1600</v>
+        <v>1633</v>
       </c>
       <c r="W768" t="s">
         <v>1203</v>
@@ -28360,7 +28606,7 @@
         <v>92</v>
       </c>
       <c r="V769" t="s">
-        <v>1600</v>
+        <v>1634</v>
       </c>
       <c r="W769" t="s">
         <v>1203</v>
@@ -28374,10 +28620,10 @@
         <v>92</v>
       </c>
       <c r="V770" t="s">
-        <v>1601</v>
+        <v>1635</v>
       </c>
       <c r="W770" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="X770" t="s">
         <v>818</v>
@@ -28388,10 +28634,10 @@
         <v>92</v>
       </c>
       <c r="V771" t="s">
-        <v>1601</v>
+        <v>1637</v>
       </c>
       <c r="W771" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="X771" t="s">
         <v>818</v>
@@ -28402,10 +28648,10 @@
         <v>92</v>
       </c>
       <c r="V772" t="s">
-        <v>1601</v>
+        <v>1638</v>
       </c>
       <c r="W772" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="X772" t="s">
         <v>818</v>
@@ -28416,7 +28662,7 @@
         <v>92</v>
       </c>
       <c r="V773" t="s">
-        <v>1603</v>
+        <v>1639</v>
       </c>
       <c r="W773" t="s">
         <v>795</v>
@@ -28430,7 +28676,7 @@
         <v>92</v>
       </c>
       <c r="V774" t="s">
-        <v>1603</v>
+        <v>1640</v>
       </c>
       <c r="W774" t="s">
         <v>795</v>
@@ -28444,7 +28690,7 @@
         <v>92</v>
       </c>
       <c r="V775" t="s">
-        <v>1603</v>
+        <v>1641</v>
       </c>
       <c r="W775" t="s">
         <v>795</v>
@@ -28458,10 +28704,10 @@
         <v>92</v>
       </c>
       <c r="V776" t="s">
-        <v>1604</v>
+        <v>1642</v>
       </c>
       <c r="W776" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
       <c r="X776" t="s">
         <v>818</v>
@@ -28472,10 +28718,10 @@
         <v>92</v>
       </c>
       <c r="V777" t="s">
-        <v>1604</v>
+        <v>1644</v>
       </c>
       <c r="W777" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
       <c r="X777" t="s">
         <v>818</v>
@@ -28486,10 +28732,10 @@
         <v>92</v>
       </c>
       <c r="V778" t="s">
-        <v>1604</v>
+        <v>1645</v>
       </c>
       <c r="W778" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
       <c r="X778" t="s">
         <v>818</v>
@@ -28500,10 +28746,10 @@
         <v>92</v>
       </c>
       <c r="V779" t="s">
-        <v>1606</v>
+        <v>1646</v>
       </c>
       <c r="W779" t="s">
-        <v>1607</v>
+        <v>1647</v>
       </c>
       <c r="X779" t="s">
         <v>818</v>
@@ -28514,10 +28760,10 @@
         <v>92</v>
       </c>
       <c r="V780" t="s">
-        <v>1606</v>
+        <v>1648</v>
       </c>
       <c r="W780" t="s">
-        <v>1607</v>
+        <v>1647</v>
       </c>
       <c r="X780" t="s">
         <v>818</v>
@@ -28528,10 +28774,10 @@
         <v>92</v>
       </c>
       <c r="V781" t="s">
-        <v>1606</v>
+        <v>1649</v>
       </c>
       <c r="W781" t="s">
-        <v>1607</v>
+        <v>1647</v>
       </c>
       <c r="X781" t="s">
         <v>818</v>
@@ -28542,10 +28788,10 @@
         <v>92</v>
       </c>
       <c r="V782" t="s">
-        <v>1608</v>
+        <v>1650</v>
       </c>
       <c r="W782" t="s">
-        <v>1609</v>
+        <v>1651</v>
       </c>
       <c r="X782" t="s">
         <v>818</v>
@@ -28556,10 +28802,10 @@
         <v>92</v>
       </c>
       <c r="V783" t="s">
-        <v>1608</v>
+        <v>1652</v>
       </c>
       <c r="W783" t="s">
-        <v>1609</v>
+        <v>1651</v>
       </c>
       <c r="X783" t="s">
         <v>818</v>
@@ -28570,10 +28816,10 @@
         <v>92</v>
       </c>
       <c r="V784" t="s">
-        <v>1608</v>
+        <v>1653</v>
       </c>
       <c r="W784" t="s">
-        <v>1609</v>
+        <v>1651</v>
       </c>
       <c r="X784" t="s">
         <v>818</v>
@@ -28584,7 +28830,7 @@
         <v>92</v>
       </c>
       <c r="V785" t="s">
-        <v>1610</v>
+        <v>1654</v>
       </c>
       <c r="W785" t="s">
         <v>758</v>
@@ -28598,7 +28844,7 @@
         <v>92</v>
       </c>
       <c r="V786" t="s">
-        <v>1610</v>
+        <v>1655</v>
       </c>
       <c r="W786" t="s">
         <v>758</v>
@@ -28612,7 +28858,7 @@
         <v>92</v>
       </c>
       <c r="V787" t="s">
-        <v>1610</v>
+        <v>1656</v>
       </c>
       <c r="W787" t="s">
         <v>758</v>
@@ -28626,10 +28872,10 @@
         <v>92</v>
       </c>
       <c r="V788" t="s">
-        <v>1611</v>
+        <v>1657</v>
       </c>
       <c r="W788" t="s">
-        <v>1612</v>
+        <v>1658</v>
       </c>
       <c r="X788" t="s">
         <v>818</v>
@@ -28640,10 +28886,10 @@
         <v>92</v>
       </c>
       <c r="V789" t="s">
-        <v>1611</v>
+        <v>1659</v>
       </c>
       <c r="W789" t="s">
-        <v>1612</v>
+        <v>1658</v>
       </c>
       <c r="X789" t="s">
         <v>818</v>
@@ -28654,10 +28900,10 @@
         <v>92</v>
       </c>
       <c r="V790" t="s">
-        <v>1611</v>
+        <v>1660</v>
       </c>
       <c r="W790" t="s">
-        <v>1612</v>
+        <v>1658</v>
       </c>
       <c r="X790" t="s">
         <v>818</v>
@@ -28668,7 +28914,7 @@
         <v>92</v>
       </c>
       <c r="V791" t="s">
-        <v>1613</v>
+        <v>1661</v>
       </c>
       <c r="W791" t="s">
         <v>744</v>
@@ -28682,7 +28928,7 @@
         <v>92</v>
       </c>
       <c r="V792" t="s">
-        <v>1613</v>
+        <v>1662</v>
       </c>
       <c r="W792" t="s">
         <v>744</v>
@@ -28696,7 +28942,7 @@
         <v>92</v>
       </c>
       <c r="V793" t="s">
-        <v>1613</v>
+        <v>1663</v>
       </c>
       <c r="W793" t="s">
         <v>744</v>
@@ -28710,10 +28956,10 @@
         <v>92</v>
       </c>
       <c r="V794" t="s">
-        <v>1614</v>
+        <v>1664</v>
       </c>
       <c r="W794" t="s">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="X794" t="s">
         <v>818</v>
@@ -28724,10 +28970,10 @@
         <v>92</v>
       </c>
       <c r="V795" t="s">
-        <v>1614</v>
+        <v>1666</v>
       </c>
       <c r="W795" t="s">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="X795" t="s">
         <v>818</v>
@@ -28738,10 +28984,10 @@
         <v>92</v>
       </c>
       <c r="V796" t="s">
-        <v>1614</v>
+        <v>1667</v>
       </c>
       <c r="W796" t="s">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="X796" t="s">
         <v>818</v>
@@ -28752,7 +28998,7 @@
         <v>92</v>
       </c>
       <c r="V797" t="s">
-        <v>1616</v>
+        <v>1668</v>
       </c>
       <c r="W797" t="s">
         <v>794</v>
@@ -28766,7 +29012,7 @@
         <v>92</v>
       </c>
       <c r="V798" t="s">
-        <v>1616</v>
+        <v>1669</v>
       </c>
       <c r="W798" t="s">
         <v>794</v>
@@ -28780,7 +29026,7 @@
         <v>92</v>
       </c>
       <c r="V799" t="s">
-        <v>1616</v>
+        <v>1670</v>
       </c>
       <c r="W799" t="s">
         <v>794</v>
@@ -28794,10 +29040,10 @@
         <v>92</v>
       </c>
       <c r="V800" t="s">
-        <v>1617</v>
+        <v>1671</v>
       </c>
       <c r="W800" t="s">
-        <v>1618</v>
+        <v>1672</v>
       </c>
       <c r="X800" t="s">
         <v>818</v>
@@ -28808,10 +29054,10 @@
         <v>92</v>
       </c>
       <c r="V801" t="s">
-        <v>1617</v>
+        <v>1673</v>
       </c>
       <c r="W801" t="s">
-        <v>1618</v>
+        <v>1672</v>
       </c>
       <c r="X801" t="s">
         <v>818</v>
@@ -28822,10 +29068,10 @@
         <v>92</v>
       </c>
       <c r="V802" t="s">
-        <v>1617</v>
+        <v>1674</v>
       </c>
       <c r="W802" t="s">
-        <v>1618</v>
+        <v>1672</v>
       </c>
       <c r="X802" t="s">
         <v>818</v>
@@ -28836,10 +29082,10 @@
         <v>92</v>
       </c>
       <c r="V803" t="s">
-        <v>1619</v>
+        <v>1675</v>
       </c>
       <c r="W803" t="s">
-        <v>1620</v>
+        <v>1676</v>
       </c>
       <c r="X803" t="s">
         <v>818</v>
@@ -28850,10 +29096,10 @@
         <v>92</v>
       </c>
       <c r="V804" t="s">
-        <v>1619</v>
+        <v>1677</v>
       </c>
       <c r="W804" t="s">
-        <v>1620</v>
+        <v>1676</v>
       </c>
       <c r="X804" t="s">
         <v>818</v>
@@ -28864,10 +29110,10 @@
         <v>92</v>
       </c>
       <c r="V805" t="s">
-        <v>1619</v>
+        <v>1678</v>
       </c>
       <c r="W805" t="s">
-        <v>1620</v>
+        <v>1676</v>
       </c>
       <c r="X805" t="s">
         <v>818</v>
@@ -28878,10 +29124,10 @@
         <v>92</v>
       </c>
       <c r="V806" t="s">
-        <v>1621</v>
+        <v>1679</v>
       </c>
       <c r="W806" t="s">
-        <v>1622</v>
+        <v>1680</v>
       </c>
       <c r="X806" t="s">
         <v>818</v>
@@ -28892,10 +29138,10 @@
         <v>92</v>
       </c>
       <c r="V807" t="s">
-        <v>1621</v>
+        <v>1681</v>
       </c>
       <c r="W807" t="s">
-        <v>1622</v>
+        <v>1680</v>
       </c>
       <c r="X807" t="s">
         <v>818</v>
@@ -28906,10 +29152,10 @@
         <v>92</v>
       </c>
       <c r="V808" t="s">
-        <v>1621</v>
+        <v>1682</v>
       </c>
       <c r="W808" t="s">
-        <v>1622</v>
+        <v>1680</v>
       </c>
       <c r="X808" t="s">
         <v>818</v>
@@ -28920,10 +29166,10 @@
         <v>92</v>
       </c>
       <c r="V809" t="s">
-        <v>1623</v>
+        <v>1683</v>
       </c>
       <c r="W809" t="s">
-        <v>1624</v>
+        <v>1684</v>
       </c>
       <c r="X809" t="s">
         <v>818</v>
@@ -28934,10 +29180,10 @@
         <v>92</v>
       </c>
       <c r="V810" t="s">
-        <v>1623</v>
+        <v>1685</v>
       </c>
       <c r="W810" t="s">
-        <v>1624</v>
+        <v>1684</v>
       </c>
       <c r="X810" t="s">
         <v>818</v>
@@ -28948,10 +29194,10 @@
         <v>92</v>
       </c>
       <c r="V811" t="s">
-        <v>1623</v>
+        <v>1686</v>
       </c>
       <c r="W811" t="s">
-        <v>1624</v>
+        <v>1684</v>
       </c>
       <c r="X811" t="s">
         <v>818</v>
@@ -28962,7 +29208,7 @@
         <v>92</v>
       </c>
       <c r="V812" t="s">
-        <v>1625</v>
+        <v>1687</v>
       </c>
       <c r="W812" t="s">
         <v>817</v>
@@ -28976,7 +29222,7 @@
         <v>92</v>
       </c>
       <c r="V813" t="s">
-        <v>1625</v>
+        <v>1688</v>
       </c>
       <c r="W813" t="s">
         <v>817</v>
@@ -28990,7 +29236,7 @@
         <v>92</v>
       </c>
       <c r="V814" t="s">
-        <v>1625</v>
+        <v>1689</v>
       </c>
       <c r="W814" t="s">
         <v>817</v>
@@ -29004,10 +29250,10 @@
         <v>92</v>
       </c>
       <c r="V815" t="s">
-        <v>1626</v>
+        <v>1690</v>
       </c>
       <c r="W815" t="s">
-        <v>1627</v>
+        <v>1691</v>
       </c>
       <c r="X815" t="s">
         <v>818</v>
@@ -29018,10 +29264,10 @@
         <v>92</v>
       </c>
       <c r="V816" t="s">
-        <v>1626</v>
+        <v>1692</v>
       </c>
       <c r="W816" t="s">
-        <v>1627</v>
+        <v>1691</v>
       </c>
       <c r="X816" t="s">
         <v>818</v>
@@ -29032,10 +29278,10 @@
         <v>92</v>
       </c>
       <c r="V817" t="s">
-        <v>1626</v>
+        <v>1693</v>
       </c>
       <c r="W817" t="s">
-        <v>1627</v>
+        <v>1691</v>
       </c>
       <c r="X817" t="s">
         <v>818</v>
@@ -29046,7 +29292,7 @@
         <v>92</v>
       </c>
       <c r="V818" t="s">
-        <v>1628</v>
+        <v>1694</v>
       </c>
       <c r="W818" t="s">
         <v>914</v>
@@ -29060,7 +29306,7 @@
         <v>92</v>
       </c>
       <c r="V819" t="s">
-        <v>1628</v>
+        <v>1695</v>
       </c>
       <c r="W819" t="s">
         <v>914</v>
@@ -29074,7 +29320,7 @@
         <v>92</v>
       </c>
       <c r="V820" t="s">
-        <v>1628</v>
+        <v>1696</v>
       </c>
       <c r="W820" t="s">
         <v>914</v>
@@ -29088,10 +29334,10 @@
         <v>92</v>
       </c>
       <c r="V821" t="s">
-        <v>1629</v>
+        <v>1697</v>
       </c>
       <c r="W821" t="s">
-        <v>1630</v>
+        <v>1698</v>
       </c>
       <c r="X821" t="s">
         <v>818</v>
@@ -29102,10 +29348,10 @@
         <v>92</v>
       </c>
       <c r="V822" t="s">
-        <v>1629</v>
+        <v>1699</v>
       </c>
       <c r="W822" t="s">
-        <v>1630</v>
+        <v>1698</v>
       </c>
       <c r="X822" t="s">
         <v>818</v>
@@ -29116,10 +29362,10 @@
         <v>92</v>
       </c>
       <c r="V823" t="s">
-        <v>1629</v>
+        <v>1700</v>
       </c>
       <c r="W823" t="s">
-        <v>1630</v>
+        <v>1698</v>
       </c>
       <c r="X823" t="s">
         <v>818</v>
@@ -29130,7 +29376,7 @@
         <v>92</v>
       </c>
       <c r="V824" t="s">
-        <v>1631</v>
+        <v>1701</v>
       </c>
       <c r="W824" t="s">
         <v>970</v>
@@ -29144,7 +29390,7 @@
         <v>92</v>
       </c>
       <c r="V825" t="s">
-        <v>1631</v>
+        <v>1702</v>
       </c>
       <c r="W825" t="s">
         <v>970</v>
@@ -29158,7 +29404,7 @@
         <v>92</v>
       </c>
       <c r="V826" t="s">
-        <v>1631</v>
+        <v>1703</v>
       </c>
       <c r="W826" t="s">
         <v>970</v>
@@ -29172,10 +29418,10 @@
         <v>92</v>
       </c>
       <c r="V827" t="s">
-        <v>1632</v>
+        <v>1704</v>
       </c>
       <c r="W827" t="s">
-        <v>1633</v>
+        <v>1705</v>
       </c>
       <c r="X827" t="s">
         <v>818</v>
@@ -29186,10 +29432,10 @@
         <v>92</v>
       </c>
       <c r="V828" t="s">
-        <v>1632</v>
+        <v>1706</v>
       </c>
       <c r="W828" t="s">
-        <v>1633</v>
+        <v>1705</v>
       </c>
       <c r="X828" t="s">
         <v>818</v>
@@ -29200,10 +29446,10 @@
         <v>92</v>
       </c>
       <c r="V829" t="s">
-        <v>1632</v>
+        <v>1707</v>
       </c>
       <c r="W829" t="s">
-        <v>1633</v>
+        <v>1705</v>
       </c>
       <c r="X829" t="s">
         <v>818</v>
@@ -29214,10 +29460,10 @@
         <v>92</v>
       </c>
       <c r="V830" t="s">
-        <v>1634</v>
+        <v>1708</v>
       </c>
       <c r="W830" t="s">
-        <v>1635</v>
+        <v>1709</v>
       </c>
       <c r="X830" t="s">
         <v>818</v>
@@ -29228,10 +29474,10 @@
         <v>92</v>
       </c>
       <c r="V831" t="s">
-        <v>1634</v>
+        <v>1710</v>
       </c>
       <c r="W831" t="s">
-        <v>1635</v>
+        <v>1709</v>
       </c>
       <c r="X831" t="s">
         <v>818</v>
@@ -29242,10 +29488,10 @@
         <v>92</v>
       </c>
       <c r="V832" t="s">
-        <v>1634</v>
+        <v>1711</v>
       </c>
       <c r="W832" t="s">
-        <v>1635</v>
+        <v>1709</v>
       </c>
       <c r="X832" t="s">
         <v>818</v>
@@ -29256,10 +29502,10 @@
         <v>92</v>
       </c>
       <c r="V833" t="s">
-        <v>1636</v>
+        <v>1712</v>
       </c>
       <c r="W833" t="s">
-        <v>1637</v>
+        <v>1713</v>
       </c>
       <c r="X833" t="s">
         <v>818</v>
@@ -29270,10 +29516,10 @@
         <v>92</v>
       </c>
       <c r="V834" t="s">
-        <v>1636</v>
+        <v>1714</v>
       </c>
       <c r="W834" t="s">
-        <v>1637</v>
+        <v>1713</v>
       </c>
       <c r="X834" t="s">
         <v>818</v>
@@ -29284,10 +29530,10 @@
         <v>92</v>
       </c>
       <c r="V835" t="s">
-        <v>1636</v>
+        <v>1715</v>
       </c>
       <c r="W835" t="s">
-        <v>1637</v>
+        <v>1713</v>
       </c>
       <c r="X835" t="s">
         <v>818</v>
@@ -29298,10 +29544,10 @@
         <v>92</v>
       </c>
       <c r="V836" t="s">
-        <v>1638</v>
+        <v>1716</v>
       </c>
       <c r="W836" t="s">
-        <v>1639</v>
+        <v>1717</v>
       </c>
       <c r="X836" t="s">
         <v>818</v>
@@ -29312,10 +29558,10 @@
         <v>92</v>
       </c>
       <c r="V837" t="s">
-        <v>1638</v>
+        <v>1718</v>
       </c>
       <c r="W837" t="s">
-        <v>1639</v>
+        <v>1717</v>
       </c>
       <c r="X837" t="s">
         <v>818</v>
@@ -29326,10 +29572,10 @@
         <v>92</v>
       </c>
       <c r="V838" t="s">
-        <v>1638</v>
+        <v>1719</v>
       </c>
       <c r="W838" t="s">
-        <v>1639</v>
+        <v>1717</v>
       </c>
       <c r="X838" t="s">
         <v>818</v>
@@ -29340,10 +29586,10 @@
         <v>92</v>
       </c>
       <c r="V839" t="s">
-        <v>1640</v>
+        <v>1720</v>
       </c>
       <c r="W839" t="s">
-        <v>1641</v>
+        <v>1721</v>
       </c>
       <c r="X839" t="s">
         <v>818</v>
@@ -29354,10 +29600,10 @@
         <v>92</v>
       </c>
       <c r="V840" t="s">
-        <v>1640</v>
+        <v>1722</v>
       </c>
       <c r="W840" t="s">
-        <v>1641</v>
+        <v>1721</v>
       </c>
       <c r="X840" t="s">
         <v>818</v>
@@ -29368,10 +29614,10 @@
         <v>92</v>
       </c>
       <c r="V841" t="s">
-        <v>1640</v>
+        <v>1723</v>
       </c>
       <c r="W841" t="s">
-        <v>1641</v>
+        <v>1721</v>
       </c>
       <c r="X841" t="s">
         <v>818</v>
@@ -29382,7 +29628,7 @@
         <v>92</v>
       </c>
       <c r="V842" t="s">
-        <v>1642</v>
+        <v>1724</v>
       </c>
       <c r="W842" t="s">
         <v>761</v>
@@ -29396,7 +29642,7 @@
         <v>92</v>
       </c>
       <c r="V843" t="s">
-        <v>1643</v>
+        <v>1725</v>
       </c>
       <c r="W843" t="s">
         <v>761</v>
@@ -29410,7 +29656,7 @@
         <v>92</v>
       </c>
       <c r="V844" t="s">
-        <v>1644</v>
+        <v>1726</v>
       </c>
       <c r="W844" t="s">
         <v>740</v>
@@ -29424,7 +29670,7 @@
         <v>92</v>
       </c>
       <c r="V845" t="s">
-        <v>1645</v>
+        <v>1727</v>
       </c>
       <c r="W845" t="s">
         <v>740</v>
@@ -29438,10 +29684,10 @@
         <v>92</v>
       </c>
       <c r="V846" t="s">
-        <v>1646</v>
+        <v>1728</v>
       </c>
       <c r="W846" t="s">
-        <v>1647</v>
+        <v>1729</v>
       </c>
       <c r="X846" t="s">
         <v>818</v>
@@ -29452,10 +29698,10 @@
         <v>92</v>
       </c>
       <c r="V847" t="s">
-        <v>1648</v>
+        <v>1730</v>
       </c>
       <c r="W847" t="s">
-        <v>1647</v>
+        <v>1729</v>
       </c>
       <c r="X847" t="s">
         <v>818</v>
@@ -29466,7 +29712,7 @@
         <v>92</v>
       </c>
       <c r="V848" t="s">
-        <v>1649</v>
+        <v>1731</v>
       </c>
       <c r="W848" t="s">
         <v>735</v>
@@ -29480,7 +29726,7 @@
         <v>92</v>
       </c>
       <c r="V849" t="s">
-        <v>1650</v>
+        <v>1732</v>
       </c>
       <c r="W849" t="s">
         <v>735</v>
@@ -29494,7 +29740,7 @@
         <v>92</v>
       </c>
       <c r="V850" t="s">
-        <v>1651</v>
+        <v>1733</v>
       </c>
       <c r="W850" t="s">
         <v>764</v>
@@ -29508,7 +29754,7 @@
         <v>92</v>
       </c>
       <c r="V851" t="s">
-        <v>1652</v>
+        <v>1734</v>
       </c>
       <c r="W851" t="s">
         <v>764</v>
@@ -29522,7 +29768,7 @@
         <v>92</v>
       </c>
       <c r="V852" t="s">
-        <v>1653</v>
+        <v>1735</v>
       </c>
       <c r="W852" t="s">
         <v>817</v>
@@ -29536,7 +29782,7 @@
         <v>92</v>
       </c>
       <c r="V853" t="s">
-        <v>1654</v>
+        <v>1736</v>
       </c>
       <c r="W853" t="s">
         <v>817</v>
@@ -29550,7 +29796,7 @@
         <v>92</v>
       </c>
       <c r="V854" t="s">
-        <v>1655</v>
+        <v>1737</v>
       </c>
       <c r="W854" t="s">
         <v>790</v>
@@ -29564,7 +29810,7 @@
         <v>92</v>
       </c>
       <c r="V855" t="s">
-        <v>1656</v>
+        <v>1738</v>
       </c>
       <c r="W855" t="s">
         <v>790</v>
@@ -29578,7 +29824,7 @@
         <v>92</v>
       </c>
       <c r="V856" t="s">
-        <v>1657</v>
+        <v>1739</v>
       </c>
       <c r="W856" t="s">
         <v>766</v>
@@ -29592,7 +29838,7 @@
         <v>92</v>
       </c>
       <c r="V857" t="s">
-        <v>1658</v>
+        <v>1740</v>
       </c>
       <c r="W857" t="s">
         <v>766</v>
@@ -29606,7 +29852,7 @@
         <v>92</v>
       </c>
       <c r="V858" t="s">
-        <v>1659</v>
+        <v>1741</v>
       </c>
       <c r="W858" t="s">
         <v>858</v>
@@ -29620,7 +29866,7 @@
         <v>92</v>
       </c>
       <c r="V859" t="s">
-        <v>1660</v>
+        <v>1742</v>
       </c>
       <c r="W859" t="s">
         <v>858</v>
@@ -29634,7 +29880,7 @@
         <v>92</v>
       </c>
       <c r="V860" t="s">
-        <v>1661</v>
+        <v>1743</v>
       </c>
       <c r="W860" t="s">
         <v>872</v>
@@ -29648,7 +29894,7 @@
         <v>92</v>
       </c>
       <c r="V861" t="s">
-        <v>1662</v>
+        <v>1744</v>
       </c>
       <c r="W861" t="s">
         <v>872</v>
@@ -29662,7 +29908,7 @@
         <v>92</v>
       </c>
       <c r="V862" t="s">
-        <v>1663</v>
+        <v>1745</v>
       </c>
       <c r="W862" t="s">
         <v>886</v>
@@ -29676,7 +29922,7 @@
         <v>92</v>
       </c>
       <c r="V863" t="s">
-        <v>1664</v>
+        <v>1746</v>
       </c>
       <c r="W863" t="s">
         <v>886</v>
@@ -29690,7 +29936,7 @@
         <v>92</v>
       </c>
       <c r="V864" t="s">
-        <v>1665</v>
+        <v>1747</v>
       </c>
       <c r="W864" t="s">
         <v>900</v>
@@ -29704,7 +29950,7 @@
         <v>92</v>
       </c>
       <c r="V865" t="s">
-        <v>1666</v>
+        <v>1748</v>
       </c>
       <c r="W865" t="s">
         <v>900</v>
@@ -29718,7 +29964,7 @@
         <v>92</v>
       </c>
       <c r="V866" t="s">
-        <v>1667</v>
+        <v>1749</v>
       </c>
       <c r="W866" t="s">
         <v>914</v>
@@ -29732,7 +29978,7 @@
         <v>92</v>
       </c>
       <c r="V867" t="s">
-        <v>1668</v>
+        <v>1750</v>
       </c>
       <c r="W867" t="s">
         <v>914</v>
@@ -29746,7 +29992,7 @@
         <v>92</v>
       </c>
       <c r="V868" t="s">
-        <v>1669</v>
+        <v>1751</v>
       </c>
       <c r="W868" t="s">
         <v>928</v>
@@ -29760,7 +30006,7 @@
         <v>92</v>
       </c>
       <c r="V869" t="s">
-        <v>1670</v>
+        <v>1752</v>
       </c>
       <c r="W869" t="s">
         <v>928</v>
@@ -29774,7 +30020,7 @@
         <v>92</v>
       </c>
       <c r="V870" t="s">
-        <v>1671</v>
+        <v>1753</v>
       </c>
       <c r="W870" t="s">
         <v>942</v>
@@ -29788,7 +30034,7 @@
         <v>92</v>
       </c>
       <c r="V871" t="s">
-        <v>1672</v>
+        <v>1754</v>
       </c>
       <c r="W871" t="s">
         <v>942</v>
@@ -29802,7 +30048,7 @@
         <v>92</v>
       </c>
       <c r="V872" t="s">
-        <v>1673</v>
+        <v>1755</v>
       </c>
       <c r="W872" t="s">
         <v>956</v>
@@ -29816,7 +30062,7 @@
         <v>92</v>
       </c>
       <c r="V873" t="s">
-        <v>1674</v>
+        <v>1756</v>
       </c>
       <c r="W873" t="s">
         <v>956</v>
@@ -29830,7 +30076,7 @@
         <v>92</v>
       </c>
       <c r="V874" t="s">
-        <v>1675</v>
+        <v>1757</v>
       </c>
       <c r="W874" t="s">
         <v>970</v>
@@ -29844,7 +30090,7 @@
         <v>92</v>
       </c>
       <c r="V875" t="s">
-        <v>1676</v>
+        <v>1758</v>
       </c>
       <c r="W875" t="s">
         <v>970</v>
@@ -29858,7 +30104,7 @@
         <v>92</v>
       </c>
       <c r="V876" t="s">
-        <v>1677</v>
+        <v>1759</v>
       </c>
       <c r="W876" t="s">
         <v>984</v>
@@ -29872,7 +30118,7 @@
         <v>92</v>
       </c>
       <c r="V877" t="s">
-        <v>1678</v>
+        <v>1760</v>
       </c>
       <c r="W877" t="s">
         <v>984</v>
@@ -29886,7 +30132,7 @@
         <v>92</v>
       </c>
       <c r="V878" t="s">
-        <v>1679</v>
+        <v>1761</v>
       </c>
       <c r="W878" t="s">
         <v>773</v>
@@ -29900,7 +30146,7 @@
         <v>92</v>
       </c>
       <c r="V879" t="s">
-        <v>1680</v>
+        <v>1762</v>
       </c>
       <c r="W879" t="s">
         <v>773</v>
@@ -29914,7 +30160,7 @@
         <v>92</v>
       </c>
       <c r="V880" t="s">
-        <v>1681</v>
+        <v>1763</v>
       </c>
       <c r="W880" t="s">
         <v>772</v>
@@ -29928,7 +30174,7 @@
         <v>92</v>
       </c>
       <c r="V881" t="s">
-        <v>1682</v>
+        <v>1764</v>
       </c>
       <c r="W881" t="s">
         <v>772</v>
@@ -29942,7 +30188,7 @@
         <v>92</v>
       </c>
       <c r="V882" t="s">
-        <v>1683</v>
+        <v>1765</v>
       </c>
       <c r="W882" t="s">
         <v>1024</v>
@@ -29956,7 +30202,7 @@
         <v>92</v>
       </c>
       <c r="V883" t="s">
-        <v>1684</v>
+        <v>1766</v>
       </c>
       <c r="W883" t="s">
         <v>1024</v>
@@ -29970,7 +30216,7 @@
         <v>92</v>
       </c>
       <c r="V884" t="s">
-        <v>1685</v>
+        <v>1767</v>
       </c>
       <c r="W884" t="s">
         <v>1038</v>
@@ -29984,7 +30230,7 @@
         <v>92</v>
       </c>
       <c r="V885" t="s">
-        <v>1686</v>
+        <v>1768</v>
       </c>
       <c r="W885" t="s">
         <v>1038</v>
@@ -29998,7 +30244,7 @@
         <v>92</v>
       </c>
       <c r="V886" t="s">
-        <v>1687</v>
+        <v>1769</v>
       </c>
       <c r="W886" t="s">
         <v>1052</v>
@@ -30012,7 +30258,7 @@
         <v>92</v>
       </c>
       <c r="V887" t="s">
-        <v>1688</v>
+        <v>1770</v>
       </c>
       <c r="W887" t="s">
         <v>1052</v>
@@ -30026,7 +30272,7 @@
         <v>92</v>
       </c>
       <c r="V888" t="s">
-        <v>1689</v>
+        <v>1771</v>
       </c>
       <c r="W888" t="s">
         <v>765</v>
@@ -30040,7 +30286,7 @@
         <v>92</v>
       </c>
       <c r="V889" t="s">
-        <v>1690</v>
+        <v>1772</v>
       </c>
       <c r="W889" t="s">
         <v>765</v>
@@ -30054,7 +30300,7 @@
         <v>92</v>
       </c>
       <c r="V890" t="s">
-        <v>1691</v>
+        <v>1773</v>
       </c>
       <c r="W890" t="s">
         <v>1079</v>
@@ -30068,7 +30314,7 @@
         <v>92</v>
       </c>
       <c r="V891" t="s">
-        <v>1692</v>
+        <v>1774</v>
       </c>
       <c r="W891" t="s">
         <v>1079</v>
@@ -30082,7 +30328,7 @@
         <v>92</v>
       </c>
       <c r="V892" t="s">
-        <v>1693</v>
+        <v>1775</v>
       </c>
       <c r="W892" t="s">
         <v>1093</v>
@@ -30096,7 +30342,7 @@
         <v>92</v>
       </c>
       <c r="V893" t="s">
-        <v>1694</v>
+        <v>1776</v>
       </c>
       <c r="W893" t="s">
         <v>1093</v>
@@ -30110,7 +30356,7 @@
         <v>92</v>
       </c>
       <c r="V894" t="s">
-        <v>1695</v>
+        <v>1777</v>
       </c>
       <c r="W894" t="s">
         <v>778</v>
@@ -30124,7 +30370,7 @@
         <v>92</v>
       </c>
       <c r="V895" t="s">
-        <v>1696</v>
+        <v>1778</v>
       </c>
       <c r="W895" t="s">
         <v>778</v>
@@ -30138,7 +30384,7 @@
         <v>92</v>
       </c>
       <c r="V896" t="s">
-        <v>1697</v>
+        <v>1779</v>
       </c>
       <c r="W896" t="s">
         <v>1120</v>
@@ -30152,7 +30398,7 @@
         <v>92</v>
       </c>
       <c r="V897" t="s">
-        <v>1698</v>
+        <v>1780</v>
       </c>
       <c r="W897" t="s">
         <v>1120</v>
@@ -30166,7 +30412,7 @@
         <v>92</v>
       </c>
       <c r="V898" t="s">
-        <v>1699</v>
+        <v>1781</v>
       </c>
       <c r="W898" t="s">
         <v>1134</v>
@@ -30180,7 +30426,7 @@
         <v>92</v>
       </c>
       <c r="V899" t="s">
-        <v>1700</v>
+        <v>1782</v>
       </c>
       <c r="W899" t="s">
         <v>1134</v>
@@ -30194,7 +30440,7 @@
         <v>92</v>
       </c>
       <c r="V900" t="s">
-        <v>1701</v>
+        <v>1783</v>
       </c>
       <c r="W900" t="s">
         <v>807</v>
@@ -30208,7 +30454,7 @@
         <v>92</v>
       </c>
       <c r="V901" t="s">
-        <v>1702</v>
+        <v>1784</v>
       </c>
       <c r="W901" t="s">
         <v>807</v>
@@ -30222,7 +30468,7 @@
         <v>92</v>
       </c>
       <c r="V902" t="s">
-        <v>1703</v>
+        <v>1785</v>
       </c>
       <c r="W902" t="s">
         <v>1161</v>
@@ -30236,7 +30482,7 @@
         <v>92</v>
       </c>
       <c r="V903" t="s">
-        <v>1704</v>
+        <v>1786</v>
       </c>
       <c r="W903" t="s">
         <v>1161</v>
@@ -30250,7 +30496,7 @@
         <v>92</v>
       </c>
       <c r="V904" t="s">
-        <v>1705</v>
+        <v>1787</v>
       </c>
       <c r="W904" t="s">
         <v>1175</v>
@@ -30264,7 +30510,7 @@
         <v>92</v>
       </c>
       <c r="V905" t="s">
-        <v>1706</v>
+        <v>1788</v>
       </c>
       <c r="W905" t="s">
         <v>1175</v>
@@ -30278,7 +30524,7 @@
         <v>92</v>
       </c>
       <c r="V906" t="s">
-        <v>1707</v>
+        <v>1789</v>
       </c>
       <c r="W906" t="s">
         <v>1189</v>
@@ -30292,7 +30538,7 @@
         <v>92</v>
       </c>
       <c r="V907" t="s">
-        <v>1708</v>
+        <v>1790</v>
       </c>
       <c r="W907" t="s">
         <v>1189</v>
@@ -30306,7 +30552,7 @@
         <v>92</v>
       </c>
       <c r="V908" t="s">
-        <v>1709</v>
+        <v>1791</v>
       </c>
       <c r="W908" t="s">
         <v>1203</v>
@@ -30320,7 +30566,7 @@
         <v>92</v>
       </c>
       <c r="V909" t="s">
-        <v>1710</v>
+        <v>1792</v>
       </c>
       <c r="W909" t="s">
         <v>1203</v>
@@ -30334,7 +30580,7 @@
         <v>92</v>
       </c>
       <c r="V910" t="s">
-        <v>1711</v>
+        <v>1793</v>
       </c>
       <c r="W910" t="s">
         <v>1217</v>
@@ -30348,7 +30594,7 @@
         <v>92</v>
       </c>
       <c r="V911" t="s">
-        <v>1712</v>
+        <v>1794</v>
       </c>
       <c r="W911" t="s">
         <v>1217</v>
@@ -30362,7 +30608,7 @@
         <v>92</v>
       </c>
       <c r="V912" t="s">
-        <v>1713</v>
+        <v>1795</v>
       </c>
       <c r="W912" t="s">
         <v>787</v>
@@ -30376,7 +30622,7 @@
         <v>92</v>
       </c>
       <c r="V913" t="s">
-        <v>1714</v>
+        <v>1796</v>
       </c>
       <c r="W913" t="s">
         <v>787</v>
@@ -30390,7 +30636,7 @@
         <v>92</v>
       </c>
       <c r="V914" t="s">
-        <v>1715</v>
+        <v>1797</v>
       </c>
       <c r="W914" t="s">
         <v>1244</v>
@@ -30404,7 +30650,7 @@
         <v>92</v>
       </c>
       <c r="V915" t="s">
-        <v>1716</v>
+        <v>1798</v>
       </c>
       <c r="W915" t="s">
         <v>1244</v>
@@ -30418,7 +30664,7 @@
         <v>92</v>
       </c>
       <c r="V916" t="s">
-        <v>1717</v>
+        <v>1799</v>
       </c>
       <c r="W916" t="s">
         <v>1258</v>
@@ -30432,7 +30678,7 @@
         <v>92</v>
       </c>
       <c r="V917" t="s">
-        <v>1718</v>
+        <v>1800</v>
       </c>
       <c r="W917" t="s">
         <v>1258</v>
@@ -30446,7 +30692,7 @@
         <v>92</v>
       </c>
       <c r="V918" t="s">
-        <v>1719</v>
+        <v>1801</v>
       </c>
       <c r="W918" t="s">
         <v>1272</v>
@@ -30460,7 +30706,7 @@
         <v>92</v>
       </c>
       <c r="V919" t="s">
-        <v>1720</v>
+        <v>1802</v>
       </c>
       <c r="W919" t="s">
         <v>1272</v>
@@ -30474,7 +30720,7 @@
         <v>92</v>
       </c>
       <c r="V920" t="s">
-        <v>1721</v>
+        <v>1803</v>
       </c>
       <c r="W920" t="s">
         <v>1286</v>
@@ -30488,7 +30734,7 @@
         <v>92</v>
       </c>
       <c r="V921" t="s">
-        <v>1722</v>
+        <v>1804</v>
       </c>
       <c r="W921" t="s">
         <v>1286</v>
@@ -30502,7 +30748,7 @@
         <v>92</v>
       </c>
       <c r="V922" t="s">
-        <v>1723</v>
+        <v>1805</v>
       </c>
       <c r="W922" t="s">
         <v>794</v>
@@ -30516,7 +30762,7 @@
         <v>92</v>
       </c>
       <c r="V923" t="s">
-        <v>1724</v>
+        <v>1806</v>
       </c>
       <c r="W923" t="s">
         <v>794</v>
@@ -30530,7 +30776,7 @@
         <v>92</v>
       </c>
       <c r="V924" t="s">
-        <v>1725</v>
+        <v>1807</v>
       </c>
       <c r="W924" t="s">
         <v>1313</v>
@@ -30544,7 +30790,7 @@
         <v>92</v>
       </c>
       <c r="V925" t="s">
-        <v>1726</v>
+        <v>1808</v>
       </c>
       <c r="W925" t="s">
         <v>1313</v>
@@ -30558,7 +30804,7 @@
         <v>92</v>
       </c>
       <c r="V926" t="s">
-        <v>1727</v>
+        <v>1809</v>
       </c>
       <c r="W926" t="s">
         <v>1327</v>
@@ -30572,7 +30818,7 @@
         <v>92</v>
       </c>
       <c r="V927" t="s">
-        <v>1728</v>
+        <v>1810</v>
       </c>
       <c r="W927" t="s">
         <v>1327</v>
@@ -30586,7 +30832,7 @@
         <v>92</v>
       </c>
       <c r="V928" t="s">
-        <v>1729</v>
+        <v>1811</v>
       </c>
       <c r="W928" t="s">
         <v>1341</v>
@@ -30600,7 +30846,7 @@
         <v>92</v>
       </c>
       <c r="V929" t="s">
-        <v>1730</v>
+        <v>1812</v>
       </c>
       <c r="W929" t="s">
         <v>1341</v>
@@ -30614,7 +30860,7 @@
         <v>92</v>
       </c>
       <c r="V930" t="s">
-        <v>1731</v>
+        <v>1813</v>
       </c>
       <c r="W930" t="s">
         <v>1355</v>
@@ -30628,7 +30874,7 @@
         <v>92</v>
       </c>
       <c r="V931" t="s">
-        <v>1732</v>
+        <v>1814</v>
       </c>
       <c r="W931" t="s">
         <v>1355</v>
@@ -30642,7 +30888,7 @@
         <v>92</v>
       </c>
       <c r="V932" t="s">
-        <v>1733</v>
+        <v>1815</v>
       </c>
       <c r="W932" t="s">
         <v>1369</v>
@@ -30656,7 +30902,7 @@
         <v>92</v>
       </c>
       <c r="V933" t="s">
-        <v>1734</v>
+        <v>1816</v>
       </c>
       <c r="W933" t="s">
         <v>1369</v>
@@ -30670,7 +30916,7 @@
         <v>92</v>
       </c>
       <c r="V934" t="s">
-        <v>1735</v>
+        <v>1817</v>
       </c>
       <c r="W934" t="s">
         <v>1383</v>
@@ -30684,7 +30930,7 @@
         <v>92</v>
       </c>
       <c r="V935" t="s">
-        <v>1736</v>
+        <v>1818</v>
       </c>
       <c r="W935" t="s">
         <v>1383</v>
@@ -30698,7 +30944,7 @@
         <v>92</v>
       </c>
       <c r="V936" t="s">
-        <v>1737</v>
+        <v>1819</v>
       </c>
       <c r="W936" t="s">
         <v>769</v>
@@ -30712,7 +30958,7 @@
         <v>92</v>
       </c>
       <c r="V937" t="s">
-        <v>1738</v>
+        <v>1820</v>
       </c>
       <c r="W937" t="s">
         <v>769</v>
@@ -30726,7 +30972,7 @@
         <v>92</v>
       </c>
       <c r="V938" t="s">
-        <v>1739</v>
+        <v>1821</v>
       </c>
       <c r="W938" t="s">
         <v>1410</v>
@@ -30740,7 +30986,7 @@
         <v>92</v>
       </c>
       <c r="V939" t="s">
-        <v>1740</v>
+        <v>1822</v>
       </c>
       <c r="W939" t="s">
         <v>1410</v>
@@ -30754,7 +31000,7 @@
         <v>92</v>
       </c>
       <c r="V940" t="s">
-        <v>1741</v>
+        <v>1823</v>
       </c>
       <c r="W940" t="s">
         <v>744</v>
@@ -30768,7 +31014,7 @@
         <v>92</v>
       </c>
       <c r="V941" t="s">
-        <v>1742</v>
+        <v>1824</v>
       </c>
       <c r="W941" t="s">
         <v>744</v>
@@ -30782,7 +31028,7 @@
         <v>92</v>
       </c>
       <c r="V942" t="s">
-        <v>1743</v>
+        <v>1825</v>
       </c>
       <c r="W942" t="s">
         <v>1437</v>
@@ -30796,7 +31042,7 @@
         <v>92</v>
       </c>
       <c r="V943" t="s">
-        <v>1744</v>
+        <v>1826</v>
       </c>
       <c r="W943" t="s">
         <v>1437</v>
@@ -30810,7 +31056,7 @@
         <v>92</v>
       </c>
       <c r="V944" t="s">
-        <v>1745</v>
+        <v>1827</v>
       </c>
       <c r="W944" t="s">
         <v>784</v>
@@ -30824,7 +31070,7 @@
         <v>92</v>
       </c>
       <c r="V945" t="s">
-        <v>1746</v>
+        <v>1828</v>
       </c>
       <c r="W945" t="s">
         <v>784</v>
@@ -30838,7 +31084,7 @@
         <v>92</v>
       </c>
       <c r="V946" t="s">
-        <v>1747</v>
+        <v>1829</v>
       </c>
       <c r="W946" t="s">
         <v>1464</v>
@@ -30852,7 +31098,7 @@
         <v>92</v>
       </c>
       <c r="V947" t="s">
-        <v>1748</v>
+        <v>1830</v>
       </c>
       <c r="W947" t="s">
         <v>1464</v>
@@ -30866,7 +31112,7 @@
         <v>92</v>
       </c>
       <c r="V948" t="s">
-        <v>1749</v>
+        <v>1831</v>
       </c>
       <c r="W948" t="s">
         <v>1478</v>
@@ -30880,7 +31126,7 @@
         <v>92</v>
       </c>
       <c r="V949" t="s">
-        <v>1750</v>
+        <v>1832</v>
       </c>
       <c r="W949" t="s">
         <v>1478</v>
@@ -30894,7 +31140,7 @@
         <v>92</v>
       </c>
       <c r="V950" t="s">
-        <v>1751</v>
+        <v>1833</v>
       </c>
       <c r="W950" t="s">
         <v>789</v>
@@ -30908,7 +31154,7 @@
         <v>92</v>
       </c>
       <c r="V951" t="s">
-        <v>1752</v>
+        <v>1834</v>
       </c>
       <c r="W951" t="s">
         <v>789</v>
@@ -30922,7 +31168,7 @@
         <v>92</v>
       </c>
       <c r="V952" t="s">
-        <v>1753</v>
+        <v>1835</v>
       </c>
       <c r="W952" t="s">
         <v>771</v>
@@ -30936,7 +31182,7 @@
         <v>92</v>
       </c>
       <c r="V953" t="s">
-        <v>1754</v>
+        <v>1836</v>
       </c>
       <c r="W953" t="s">
         <v>771</v>
@@ -30950,7 +31196,7 @@
         <v>92</v>
       </c>
       <c r="V954" t="s">
-        <v>1755</v>
+        <v>1837</v>
       </c>
       <c r="W954" t="s">
         <v>1518</v>
@@ -30964,7 +31210,7 @@
         <v>92</v>
       </c>
       <c r="V955" t="s">
-        <v>1756</v>
+        <v>1838</v>
       </c>
       <c r="W955" t="s">
         <v>1518</v>
@@ -30978,7 +31224,7 @@
         <v>92</v>
       </c>
       <c r="V956" t="s">
-        <v>1757</v>
+        <v>1839</v>
       </c>
       <c r="W956" t="s">
         <v>1532</v>
@@ -30992,7 +31238,7 @@
         <v>92</v>
       </c>
       <c r="V957" t="s">
-        <v>1758</v>
+        <v>1840</v>
       </c>
       <c r="W957" t="s">
         <v>1532</v>
@@ -31006,7 +31252,7 @@
         <v>92</v>
       </c>
       <c r="V958" t="s">
-        <v>1759</v>
+        <v>1841</v>
       </c>
       <c r="W958" t="s">
         <v>1546</v>
@@ -31020,7 +31266,7 @@
         <v>92</v>
       </c>
       <c r="V959" t="s">
-        <v>1760</v>
+        <v>1842</v>
       </c>
       <c r="W959" t="s">
         <v>1546</v>
@@ -31034,7 +31280,7 @@
         <v>92</v>
       </c>
       <c r="V960" t="s">
-        <v>1761</v>
+        <v>1843</v>
       </c>
       <c r="W960" t="s">
         <v>1560</v>
@@ -31048,7 +31294,7 @@
         <v>92</v>
       </c>
       <c r="V961" t="s">
-        <v>1762</v>
+        <v>1844</v>
       </c>
       <c r="W961" t="s">
         <v>1560</v>
@@ -31062,10 +31308,10 @@
         <v>92</v>
       </c>
       <c r="V962" t="s">
-        <v>1763</v>
+        <v>1845</v>
       </c>
       <c r="W962" t="s">
-        <v>1764</v>
+        <v>1846</v>
       </c>
       <c r="X962" t="s">
         <v>818</v>
@@ -31076,10 +31322,10 @@
         <v>92</v>
       </c>
       <c r="V963" t="s">
-        <v>1765</v>
+        <v>1847</v>
       </c>
       <c r="W963" t="s">
-        <v>1764</v>
+        <v>1846</v>
       </c>
       <c r="X963" t="s">
         <v>818</v>
@@ -31090,10 +31336,10 @@
         <v>92</v>
       </c>
       <c r="V964" t="s">
-        <v>1766</v>
+        <v>1848</v>
       </c>
       <c r="W964" t="s">
-        <v>1767</v>
+        <v>1849</v>
       </c>
       <c r="X964" t="s">
         <v>818</v>
@@ -31104,10 +31350,10 @@
         <v>92</v>
       </c>
       <c r="V965" t="s">
-        <v>1768</v>
+        <v>1850</v>
       </c>
       <c r="W965" t="s">
-        <v>1767</v>
+        <v>1849</v>
       </c>
       <c r="X965" t="s">
         <v>818</v>
@@ -31118,7 +31364,7 @@
         <v>92</v>
       </c>
       <c r="V966" t="s">
-        <v>1769</v>
+        <v>1851</v>
       </c>
       <c r="W966" t="s">
         <v>754</v>
@@ -31132,7 +31378,7 @@
         <v>92</v>
       </c>
       <c r="V967" t="s">
-        <v>1770</v>
+        <v>1852</v>
       </c>
       <c r="W967" t="s">
         <v>754</v>
@@ -31146,10 +31392,10 @@
         <v>92</v>
       </c>
       <c r="V968" t="s">
-        <v>1771</v>
+        <v>1853</v>
       </c>
       <c r="W968" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="X968" t="s">
         <v>818</v>
@@ -31160,10 +31406,10 @@
         <v>92</v>
       </c>
       <c r="V969" t="s">
-        <v>1772</v>
+        <v>1854</v>
       </c>
       <c r="W969" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="X969" t="s">
         <v>818</v>
@@ -31174,10 +31420,10 @@
         <v>92</v>
       </c>
       <c r="V970" t="s">
-        <v>1773</v>
+        <v>1855</v>
       </c>
       <c r="W970" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="X970" t="s">
         <v>818</v>
@@ -31188,10 +31434,10 @@
         <v>92</v>
       </c>
       <c r="V971" t="s">
-        <v>1774</v>
+        <v>1856</v>
       </c>
       <c r="W971" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="X971" t="s">
         <v>818</v>
@@ -31202,10 +31448,10 @@
         <v>92</v>
       </c>
       <c r="V972" t="s">
-        <v>1775</v>
+        <v>1857</v>
       </c>
       <c r="W972" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="X972" t="s">
         <v>818</v>
@@ -31216,10 +31462,10 @@
         <v>92</v>
       </c>
       <c r="V973" t="s">
-        <v>1776</v>
+        <v>1858</v>
       </c>
       <c r="W973" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="X973" t="s">
         <v>818</v>
@@ -31230,10 +31476,10 @@
         <v>92</v>
       </c>
       <c r="V974" t="s">
-        <v>1777</v>
+        <v>1859</v>
       </c>
       <c r="W974" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="X974" t="s">
         <v>818</v>
@@ -31244,10 +31490,10 @@
         <v>92</v>
       </c>
       <c r="V975" t="s">
-        <v>1778</v>
+        <v>1860</v>
       </c>
       <c r="W975" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="X975" t="s">
         <v>818</v>
@@ -31258,10 +31504,10 @@
         <v>92</v>
       </c>
       <c r="V976" t="s">
-        <v>1779</v>
+        <v>1861</v>
       </c>
       <c r="W976" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="X976" t="s">
         <v>818</v>
@@ -31272,10 +31518,10 @@
         <v>92</v>
       </c>
       <c r="V977" t="s">
-        <v>1780</v>
+        <v>1862</v>
       </c>
       <c r="W977" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="X977" t="s">
         <v>818</v>
@@ -31286,7 +31532,7 @@
         <v>92</v>
       </c>
       <c r="V978" t="s">
-        <v>1781</v>
+        <v>1863</v>
       </c>
       <c r="W978" t="s">
         <v>797</v>
@@ -31300,7 +31546,7 @@
         <v>92</v>
       </c>
       <c r="V979" t="s">
-        <v>1782</v>
+        <v>1864</v>
       </c>
       <c r="W979" t="s">
         <v>797</v>
@@ -31314,10 +31560,10 @@
         <v>92</v>
       </c>
       <c r="V980" t="s">
-        <v>1783</v>
+        <v>1865</v>
       </c>
       <c r="W980" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="X980" t="s">
         <v>818</v>
@@ -31328,10 +31574,10 @@
         <v>92</v>
       </c>
       <c r="V981" t="s">
-        <v>1784</v>
+        <v>1866</v>
       </c>
       <c r="W981" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="X981" t="s">
         <v>818</v>
@@ -31342,10 +31588,10 @@
         <v>92</v>
       </c>
       <c r="V982" t="s">
-        <v>1785</v>
+        <v>1867</v>
       </c>
       <c r="W982" t="s">
-        <v>1589</v>
+        <v>1607</v>
       </c>
       <c r="X982" t="s">
         <v>818</v>
@@ -31356,10 +31602,10 @@
         <v>92</v>
       </c>
       <c r="V983" t="s">
-        <v>1786</v>
+        <v>1868</v>
       </c>
       <c r="W983" t="s">
-        <v>1589</v>
+        <v>1607</v>
       </c>
       <c r="X983" t="s">
         <v>818</v>
@@ -31370,10 +31616,10 @@
         <v>92</v>
       </c>
       <c r="V984" t="s">
-        <v>1787</v>
+        <v>1869</v>
       </c>
       <c r="W984" t="s">
-        <v>1591</v>
+        <v>1611</v>
       </c>
       <c r="X984" t="s">
         <v>818</v>
@@ -31384,10 +31630,10 @@
         <v>92</v>
       </c>
       <c r="V985" t="s">
-        <v>1788</v>
+        <v>1870</v>
       </c>
       <c r="W985" t="s">
-        <v>1591</v>
+        <v>1611</v>
       </c>
       <c r="X985" t="s">
         <v>818</v>
@@ -31398,7 +31644,7 @@
         <v>92</v>
       </c>
       <c r="V986" t="s">
-        <v>1789</v>
+        <v>1871</v>
       </c>
       <c r="W986" t="s">
         <v>811</v>
@@ -31412,7 +31658,7 @@
         <v>92</v>
       </c>
       <c r="V987" t="s">
-        <v>1790</v>
+        <v>1872</v>
       </c>
       <c r="W987" t="s">
         <v>811</v>
@@ -31426,10 +31672,10 @@
         <v>92</v>
       </c>
       <c r="V988" t="s">
-        <v>1791</v>
+        <v>1873</v>
       </c>
       <c r="W988" t="s">
-        <v>1594</v>
+        <v>1618</v>
       </c>
       <c r="X988" t="s">
         <v>818</v>
@@ -31440,10 +31686,10 @@
         <v>92</v>
       </c>
       <c r="V989" t="s">
-        <v>1792</v>
+        <v>1874</v>
       </c>
       <c r="W989" t="s">
-        <v>1594</v>
+        <v>1618</v>
       </c>
       <c r="X989" t="s">
         <v>818</v>
@@ -31454,7 +31700,7 @@
         <v>92</v>
       </c>
       <c r="V990" t="s">
-        <v>1793</v>
+        <v>1875</v>
       </c>
       <c r="W990" t="s">
         <v>788</v>
@@ -31468,7 +31714,7 @@
         <v>92</v>
       </c>
       <c r="V991" t="s">
-        <v>1794</v>
+        <v>1876</v>
       </c>
       <c r="W991" t="s">
         <v>788</v>
@@ -31482,10 +31728,10 @@
         <v>92</v>
       </c>
       <c r="V992" t="s">
-        <v>1795</v>
+        <v>1877</v>
       </c>
       <c r="W992" t="s">
-        <v>1597</v>
+        <v>1625</v>
       </c>
       <c r="X992" t="s">
         <v>818</v>
@@ -31496,10 +31742,10 @@
         <v>92</v>
       </c>
       <c r="V993" t="s">
-        <v>1796</v>
+        <v>1878</v>
       </c>
       <c r="W993" t="s">
-        <v>1597</v>
+        <v>1625</v>
       </c>
       <c r="X993" t="s">
         <v>818</v>
@@ -31510,10 +31756,10 @@
         <v>92</v>
       </c>
       <c r="V994" t="s">
-        <v>1797</v>
+        <v>1879</v>
       </c>
       <c r="W994" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="X994" t="s">
         <v>818</v>
@@ -31524,10 +31770,10 @@
         <v>92</v>
       </c>
       <c r="V995" t="s">
-        <v>1798</v>
+        <v>1880</v>
       </c>
       <c r="W995" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="X995" t="s">
         <v>818</v>
@@ -31538,10 +31784,10 @@
         <v>92</v>
       </c>
       <c r="V996" t="s">
-        <v>1799</v>
+        <v>1881</v>
       </c>
       <c r="W996" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="X996" t="s">
         <v>818</v>
@@ -31552,10 +31798,10 @@
         <v>92</v>
       </c>
       <c r="V997" t="s">
-        <v>1800</v>
+        <v>1882</v>
       </c>
       <c r="W997" t="s">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="X997" t="s">
         <v>818</v>
@@ -31566,7 +31812,7 @@
         <v>92</v>
       </c>
       <c r="V998" t="s">
-        <v>1801</v>
+        <v>1883</v>
       </c>
       <c r="W998" t="s">
         <v>795</v>
@@ -31580,7 +31826,7 @@
         <v>92</v>
       </c>
       <c r="V999" t="s">
-        <v>1802</v>
+        <v>1884</v>
       </c>
       <c r="W999" t="s">
         <v>795</v>
@@ -31594,10 +31840,10 @@
         <v>92</v>
       </c>
       <c r="V1000" t="s">
-        <v>1803</v>
+        <v>1885</v>
       </c>
       <c r="W1000" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
       <c r="X1000" t="s">
         <v>818</v>
@@ -31608,10 +31854,10 @@
         <v>92</v>
       </c>
       <c r="V1001" t="s">
-        <v>1804</v>
+        <v>1886</v>
       </c>
       <c r="W1001" t="s">
-        <v>1605</v>
+        <v>1643</v>
       </c>
       <c r="X1001" t="s">
         <v>818</v>
@@ -31622,10 +31868,10 @@
         <v>92</v>
       </c>
       <c r="V1002" t="s">
-        <v>1805</v>
+        <v>1887</v>
       </c>
       <c r="W1002" t="s">
-        <v>1607</v>
+        <v>1647</v>
       </c>
       <c r="X1002" t="s">
         <v>818</v>
@@ -31636,10 +31882,10 @@
         <v>92</v>
       </c>
       <c r="V1003" t="s">
-        <v>1806</v>
+        <v>1888</v>
       </c>
       <c r="W1003" t="s">
-        <v>1607</v>
+        <v>1647</v>
       </c>
       <c r="X1003" t="s">
         <v>818</v>
@@ -31650,10 +31896,10 @@
         <v>92</v>
       </c>
       <c r="V1004" t="s">
-        <v>1807</v>
+        <v>1889</v>
       </c>
       <c r="W1004" t="s">
-        <v>1609</v>
+        <v>1651</v>
       </c>
       <c r="X1004" t="s">
         <v>818</v>
@@ -31664,10 +31910,10 @@
         <v>92</v>
       </c>
       <c r="V1005" t="s">
-        <v>1808</v>
+        <v>1890</v>
       </c>
       <c r="W1005" t="s">
-        <v>1609</v>
+        <v>1651</v>
       </c>
       <c r="X1005" t="s">
         <v>818</v>
@@ -31678,7 +31924,7 @@
         <v>92</v>
       </c>
       <c r="V1006" t="s">
-        <v>1809</v>
+        <v>1891</v>
       </c>
       <c r="W1006" t="s">
         <v>758</v>
@@ -31692,7 +31938,7 @@
         <v>92</v>
       </c>
       <c r="V1007" t="s">
-        <v>1810</v>
+        <v>1892</v>
       </c>
       <c r="W1007" t="s">
         <v>758</v>
@@ -31706,10 +31952,10 @@
         <v>92</v>
       </c>
       <c r="V1008" t="s">
-        <v>1811</v>
+        <v>1893</v>
       </c>
       <c r="W1008" t="s">
-        <v>1612</v>
+        <v>1658</v>
       </c>
       <c r="X1008" t="s">
         <v>818</v>
@@ -31720,10 +31966,10 @@
         <v>92</v>
       </c>
       <c r="V1009" t="s">
-        <v>1812</v>
+        <v>1894</v>
       </c>
       <c r="W1009" t="s">
-        <v>1612</v>
+        <v>1658</v>
       </c>
       <c r="X1009" t="s">
         <v>818</v>
@@ -31734,10 +31980,10 @@
         <v>92</v>
       </c>
       <c r="V1010" t="s">
-        <v>1813</v>
+        <v>1895</v>
       </c>
       <c r="W1010" t="s">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="X1010" t="s">
         <v>818</v>
@@ -31748,10 +31994,10 @@
         <v>92</v>
       </c>
       <c r="V1011" t="s">
-        <v>1814</v>
+        <v>1896</v>
       </c>
       <c r="W1011" t="s">
-        <v>1615</v>
+        <v>1665</v>
       </c>
       <c r="X1011" t="s">
         <v>818</v>
@@ -31762,10 +32008,10 @@
         <v>92</v>
       </c>
       <c r="V1012" t="s">
-        <v>1815</v>
+        <v>1897</v>
       </c>
       <c r="W1012" t="s">
-        <v>1618</v>
+        <v>1672</v>
       </c>
       <c r="X1012" t="s">
         <v>818</v>
@@ -31776,10 +32022,10 @@
         <v>92</v>
       </c>
       <c r="V1013" t="s">
-        <v>1816</v>
+        <v>1898</v>
       </c>
       <c r="W1013" t="s">
-        <v>1618</v>
+        <v>1672</v>
       </c>
       <c r="X1013" t="s">
         <v>818</v>
@@ -31790,10 +32036,10 @@
         <v>92</v>
       </c>
       <c r="V1014" t="s">
-        <v>1817</v>
+        <v>1899</v>
       </c>
       <c r="W1014" t="s">
-        <v>1620</v>
+        <v>1676</v>
       </c>
       <c r="X1014" t="s">
         <v>818</v>
@@ -31804,10 +32050,10 @@
         <v>92</v>
       </c>
       <c r="V1015" t="s">
-        <v>1818</v>
+        <v>1900</v>
       </c>
       <c r="W1015" t="s">
-        <v>1620</v>
+        <v>1676</v>
       </c>
       <c r="X1015" t="s">
         <v>818</v>
@@ -31818,10 +32064,10 @@
         <v>92</v>
       </c>
       <c r="V1016" t="s">
-        <v>1819</v>
+        <v>1901</v>
       </c>
       <c r="W1016" t="s">
-        <v>1622</v>
+        <v>1680</v>
       </c>
       <c r="X1016" t="s">
         <v>818</v>
@@ -31832,10 +32078,10 @@
         <v>92</v>
       </c>
       <c r="V1017" t="s">
-        <v>1820</v>
+        <v>1902</v>
       </c>
       <c r="W1017" t="s">
-        <v>1622</v>
+        <v>1680</v>
       </c>
       <c r="X1017" t="s">
         <v>818</v>
@@ -31846,10 +32092,10 @@
         <v>92</v>
       </c>
       <c r="V1018" t="s">
-        <v>1821</v>
+        <v>1903</v>
       </c>
       <c r="W1018" t="s">
-        <v>1624</v>
+        <v>1684</v>
       </c>
       <c r="X1018" t="s">
         <v>818</v>
@@ -31860,10 +32106,10 @@
         <v>92</v>
       </c>
       <c r="V1019" t="s">
-        <v>1822</v>
+        <v>1904</v>
       </c>
       <c r="W1019" t="s">
-        <v>1624</v>
+        <v>1684</v>
       </c>
       <c r="X1019" t="s">
         <v>818</v>
@@ -31874,10 +32120,10 @@
         <v>92</v>
       </c>
       <c r="V1020" t="s">
-        <v>1823</v>
+        <v>1905</v>
       </c>
       <c r="W1020" t="s">
-        <v>1627</v>
+        <v>1691</v>
       </c>
       <c r="X1020" t="s">
         <v>818</v>
@@ -31888,10 +32134,10 @@
         <v>92</v>
       </c>
       <c r="V1021" t="s">
-        <v>1824</v>
+        <v>1906</v>
       </c>
       <c r="W1021" t="s">
-        <v>1627</v>
+        <v>1691</v>
       </c>
       <c r="X1021" t="s">
         <v>818</v>
@@ -31902,10 +32148,10 @@
         <v>92</v>
       </c>
       <c r="V1022" t="s">
-        <v>1825</v>
+        <v>1907</v>
       </c>
       <c r="W1022" t="s">
-        <v>1630</v>
+        <v>1698</v>
       </c>
       <c r="X1022" t="s">
         <v>818</v>
@@ -31916,10 +32162,10 @@
         <v>92</v>
       </c>
       <c r="V1023" t="s">
-        <v>1826</v>
+        <v>1908</v>
       </c>
       <c r="W1023" t="s">
-        <v>1630</v>
+        <v>1698</v>
       </c>
       <c r="X1023" t="s">
         <v>818</v>
@@ -31930,10 +32176,10 @@
         <v>92</v>
       </c>
       <c r="V1024" t="s">
-        <v>1827</v>
+        <v>1909</v>
       </c>
       <c r="W1024" t="s">
-        <v>1633</v>
+        <v>1705</v>
       </c>
       <c r="X1024" t="s">
         <v>818</v>
@@ -31944,10 +32190,10 @@
         <v>92</v>
       </c>
       <c r="V1025" t="s">
-        <v>1828</v>
+        <v>1910</v>
       </c>
       <c r="W1025" t="s">
-        <v>1633</v>
+        <v>1705</v>
       </c>
       <c r="X1025" t="s">
         <v>818</v>
@@ -31958,10 +32204,10 @@
         <v>92</v>
       </c>
       <c r="V1026" t="s">
-        <v>1829</v>
+        <v>1911</v>
       </c>
       <c r="W1026" t="s">
-        <v>1635</v>
+        <v>1709</v>
       </c>
       <c r="X1026" t="s">
         <v>818</v>
@@ -31972,10 +32218,10 @@
         <v>92</v>
       </c>
       <c r="V1027" t="s">
-        <v>1830</v>
+        <v>1912</v>
       </c>
       <c r="W1027" t="s">
-        <v>1635</v>
+        <v>1709</v>
       </c>
       <c r="X1027" t="s">
         <v>818</v>
@@ -31986,10 +32232,10 @@
         <v>92</v>
       </c>
       <c r="V1028" t="s">
-        <v>1831</v>
+        <v>1913</v>
       </c>
       <c r="W1028" t="s">
-        <v>1637</v>
+        <v>1713</v>
       </c>
       <c r="X1028" t="s">
         <v>818</v>
@@ -32000,10 +32246,10 @@
         <v>92</v>
       </c>
       <c r="V1029" t="s">
-        <v>1832</v>
+        <v>1914</v>
       </c>
       <c r="W1029" t="s">
-        <v>1637</v>
+        <v>1713</v>
       </c>
       <c r="X1029" t="s">
         <v>818</v>
@@ -32014,10 +32260,10 @@
         <v>92</v>
       </c>
       <c r="V1030" t="s">
-        <v>1833</v>
+        <v>1915</v>
       </c>
       <c r="W1030" t="s">
-        <v>1639</v>
+        <v>1717</v>
       </c>
       <c r="X1030" t="s">
         <v>818</v>
@@ -32028,10 +32274,10 @@
         <v>92</v>
       </c>
       <c r="V1031" t="s">
-        <v>1834</v>
+        <v>1916</v>
       </c>
       <c r="W1031" t="s">
-        <v>1639</v>
+        <v>1717</v>
       </c>
       <c r="X1031" t="s">
         <v>818</v>
@@ -32042,10 +32288,10 @@
         <v>92</v>
       </c>
       <c r="V1032" t="s">
-        <v>1835</v>
+        <v>1917</v>
       </c>
       <c r="W1032" t="s">
-        <v>1641</v>
+        <v>1721</v>
       </c>
       <c r="X1032" t="s">
         <v>818</v>
@@ -32056,10 +32302,10 @@
         <v>92</v>
       </c>
       <c r="V1033" t="s">
-        <v>1836</v>
+        <v>1918</v>
       </c>
       <c r="W1033" t="s">
-        <v>1641</v>
+        <v>1721</v>
       </c>
       <c r="X1033" t="s">
         <v>818</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4C5BB33-A62F-4D44-B544-5F8D23550F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB8805D1-3255-495A-BC7E-4086BBD2A835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A0596EB-BC60-40BF-923C-A18B070195EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D54D46-EAA0-41B9-A60E-785D7DC83643}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB8805D1-3255-495A-BC7E-4086BBD2A835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D24B8252-5CEF-481C-9AD0-CC19FAF45357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D54D46-EAA0-41B9-A60E-785D7DC83643}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFDB851B-DADB-477A-83DD-57F0FCD7EEFA}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D24B8252-5CEF-481C-9AD0-CC19FAF45357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF708FA8-F72B-4125-B40B-82D63BCEF8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFDB851B-DADB-477A-83DD-57F0FCD7EEFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F98EB89-9910-4B04-AA52-0092B0C0E9D5}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF708FA8-F72B-4125-B40B-82D63BCEF8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{723BA93A-DF5C-43CA-B9F4-4554A15DE5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F98EB89-9910-4B04-AA52-0092B0C0E9D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D434D5-5461-4054-830E-2EF1D5107944}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{723BA93A-DF5C-43CA-B9F4-4554A15DE5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{943CCDBE-7706-4F3F-91D0-7857817F8F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D434D5-5461-4054-830E-2EF1D5107944}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48080BB1-A9E5-4E60-AF2C-35464291AED3}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{943CCDBE-7706-4F3F-91D0-7857817F8F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7FC7097-AD73-4CCB-8531-C633DE461A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48080BB1-A9E5-4E60-AF2C-35464291AED3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956AE6D0-9551-4A96-BE42-ACFEA295BD81}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7FC7097-AD73-4CCB-8531-C633DE461A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{454BACB7-B085-4FCC-991D-3C2D29E48651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956AE6D0-9551-4A96-BE42-ACFEA295BD81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8992E6-99A6-44F1-8946-0840735F745A}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{454BACB7-B085-4FCC-991D-3C2D29E48651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93EBBAEA-46F6-4CE7-9FDE-FF3CD79BA7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8992E6-99A6-44F1-8946-0840735F745A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2945DF80-ED42-422F-9E7C-63FBA9F11C5C}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93EBBAEA-46F6-4CE7-9FDE-FF3CD79BA7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0740EB13-3F42-4C91-928A-F94FEC032354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2945DF80-ED42-422F-9E7C-63FBA9F11C5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6EE83C-FEBF-4592-A2B2-A6487EFCFA00}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0740EB13-3F42-4C91-928A-F94FEC032354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5412935D-ECC0-475D-B3DF-6BB6DD0254FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6EE83C-FEBF-4592-A2B2-A6487EFCFA00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015D4A8F-CD0E-43BF-910F-74D9A8DCF8B2}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5412935D-ECC0-475D-B3DF-6BB6DD0254FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57CA23E6-EE0F-4189-859E-80169990DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015D4A8F-CD0E-43BF-910F-74D9A8DCF8B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8B4BBA-E3F6-44C9-844A-2B88B2D07F1A}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57CA23E6-EE0F-4189-859E-80169990DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36A711B9-7B51-4C55-86AC-506642C964F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8B4BBA-E3F6-44C9-844A-2B88B2D07F1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D40A6C2-AC11-4A56-9C33-D7BF303F7481}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36A711B9-7B51-4C55-86AC-506642C964F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{375B3DBA-20E8-46EE-A61F-76DB27A47075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D40A6C2-AC11-4A56-9C33-D7BF303F7481}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B160EC3-5EAF-4898-8624-19238B1397E0}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{375B3DBA-20E8-46EE-A61F-76DB27A47075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EDAC22C-817E-49D8-9B73-309E69620487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B160EC3-5EAF-4898-8624-19238B1397E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8502E973-0671-4D82-B5AC-74F0FB053247}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EDAC22C-817E-49D8-9B73-309E69620487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D06439E-23E1-4C79-BF7D-2974EA8729F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6396,7 +6396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8502E973-0671-4D82-B5AC-74F0FB053247}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30402E1-A7B0-4755-B917-631B3C65DCEA}">
   <dimension ref="B2:AI1033"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A35BA19-93CD-44E2-9C5B-DD0090428008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2246996F-9D5F-4CE5-8AF3-78F6B94C058B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0CA48C-C4C7-4AD6-90A1-89DE0A457948}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70710BA-2DAE-440F-92A5-DE4A062BBC77}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2246996F-9D5F-4CE5-8AF3-78F6B94C058B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C15380F-92C9-4D7C-A8A5-C335AC081C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70710BA-2DAE-440F-92A5-DE4A062BBC77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6909E351-DEE7-4F2C-8BB6-3C17D80E0F2E}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C15380F-92C9-4D7C-A8A5-C335AC081C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEDB6FE4-488A-4DCF-A2D4-7CA1F1111E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6909E351-DEE7-4F2C-8BB6-3C17D80E0F2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56252A0C-DF02-48E1-879C-C79F3C78DC7F}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEDB6FE4-488A-4DCF-A2D4-7CA1F1111E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DD984E9-D951-4C78-80A8-93DAD6A134C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56252A0C-DF02-48E1-879C-C79F3C78DC7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5CB3B0-1214-4C59-B4A0-277771E84053}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DD984E9-D951-4C78-80A8-93DAD6A134C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6462ED6C-CA72-4B16-A54D-4D89A82EC565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5CB3B0-1214-4C59-B4A0-277771E84053}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD4537A-C8E4-4FBD-9A24-8B7B6887F780}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6462ED6C-CA72-4B16-A54D-4D89A82EC565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B68A5C5-85BE-4DB4-BEB9-76F1FB3E8BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD4537A-C8E4-4FBD-9A24-8B7B6887F780}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A867CF1-F0DE-4E39-86F6-12466DEAA25E}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B68A5C5-85BE-4DB4-BEB9-76F1FB3E8BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34440153-1FE3-4EF6-97F3-038005345AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A867CF1-F0DE-4E39-86F6-12466DEAA25E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B4EACA-27AB-4A9E-AB3F-81B21229C981}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34440153-1FE3-4EF6-97F3-038005345AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{424CB85B-10A9-40F5-B92F-7AB0CCE42FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B4EACA-27AB-4A9E-AB3F-81B21229C981}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FC84A4-ACA0-498D-8C27-85A200920A78}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{424CB85B-10A9-40F5-B92F-7AB0CCE42FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C347AADC-D109-4A6A-A321-B930A0D82172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6630,7 +6630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FC84A4-ACA0-498D-8C27-85A200920A78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51110992-612F-4A35-8AC4-809EE8651B7A}">
   <dimension ref="B2:AI1102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C347AADC-D109-4A6A-A321-B930A0D82172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93D09E5-499E-4FEC-97AE-AFE89E837CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8497" uniqueCount="2007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8501" uniqueCount="2009">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -6135,9 +6135,6 @@
     <t>pset_set</t>
   </si>
   <si>
-    <t>ELE,DMD,PRE</t>
-  </si>
-  <si>
     <t>Trd_electricity import</t>
   </si>
   <si>
@@ -6145,6 +6142,15 @@
   </si>
   <si>
     <t>Trd_electricity export</t>
+  </si>
+  <si>
+    <t>STGOUT_BND</t>
+  </si>
+  <si>
+    <t>DMD,PRE,ELE</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
 </sst>
 </file>
@@ -6700,7 +6706,7 @@
       <c r="X3" t="s">
         <v>734</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="Z3" t="s">
         <v>411</v>
       </c>
       <c r="AG3" t="s">
@@ -6762,26 +6768,29 @@
       <c r="X4" t="s">
         <v>818</v>
       </c>
+      <c r="Z4" t="s">
+        <v>412</v>
+      </c>
       <c r="AA4" t="s">
-        <v>412</v>
+        <v>1998</v>
       </c>
       <c r="AB4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="AC4" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="AD4" t="s">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="AE4" t="s">
         <v>2002</v>
       </c>
       <c r="AG4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="AH4" t="s">
         <v>2004</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>2005</v>
       </c>
       <c r="AI4" t="s">
         <v>818</v>
@@ -6836,26 +6845,26 @@
       <c r="X5" t="s">
         <v>818</v>
       </c>
+      <c r="Z5" t="s">
+        <v>1997</v>
+      </c>
       <c r="AA5" t="s">
-        <v>1997</v>
-      </c>
-      <c r="AB5" t="s">
         <v>1999</v>
       </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
       <c r="AC5">
-        <v>2</v>
-      </c>
-      <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="AG5" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="AH5" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AI5" t="s">
         <v>736</v>
@@ -6909,6 +6918,21 @@
       </c>
       <c r="X6" t="s">
         <v>818</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>2008</v>
       </c>
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.45">
